--- a/data/PPDB database.xlsx
+++ b/data/PPDB database.xlsx
@@ -6905,7 +6905,7 @@
     <t>CoG (Region)</t>
   </si>
   <si>
-    <t>http://churchofgodinindiakeralaregion.org/public/cog-removebg.png</t>
+    <t>/media/logos/inRegion.png</t>
   </si>
   <si>
     <t>#440025</t>
@@ -12835,7 +12835,7 @@
     <t>UAECNE</t>
   </si>
   <si>
-    <t>http://www.uaecne.org/images/uaecne-logo-01.svg</t>
+    <t>/media/logos/syUAE.svg</t>
   </si>
   <si>
     <t>#ffeedc</t>
@@ -36415,7 +36415,7 @@
       <c r="H216" s="24"/>
       <c r="I216" s="24"/>
       <c r="J216" s="24"/>
-      <c r="K216" s="19" t="s">
+      <c r="K216" s="5" t="s">
         <v>1825</v>
       </c>
       <c r="L216" s="37" t="s">
@@ -53913,7 +53913,7 @@
       <c r="H410" s="24"/>
       <c r="I410" s="24"/>
       <c r="J410" s="24"/>
-      <c r="K410" s="17" t="s">
+      <c r="K410" s="5" t="s">
         <v>3302</v>
       </c>
       <c r="L410" s="5" t="s">
@@ -79330,589 +79330,587 @@
     <hyperlink r:id="rId347" ref="AJ215"/>
     <hyperlink r:id="rId348" ref="AL215"/>
     <hyperlink r:id="rId349" ref="AO215"/>
-    <hyperlink r:id="rId350" ref="K216"/>
-    <hyperlink r:id="rId351" ref="AJ216"/>
-    <hyperlink r:id="rId352" ref="AM216"/>
-    <hyperlink r:id="rId353" location="v=onepage&amp;q&amp;f=false" ref="AT216"/>
-    <hyperlink r:id="rId354" ref="K217"/>
-    <hyperlink r:id="rId355" ref="AK217"/>
-    <hyperlink r:id="rId356" ref="K218"/>
-    <hyperlink r:id="rId357" ref="AJ218"/>
-    <hyperlink r:id="rId358" ref="K219"/>
-    <hyperlink r:id="rId359" ref="AJ219"/>
-    <hyperlink r:id="rId360" ref="K220"/>
-    <hyperlink r:id="rId361" ref="AJ220"/>
-    <hyperlink r:id="rId362" ref="K221"/>
-    <hyperlink r:id="rId363" ref="AJ221"/>
-    <hyperlink r:id="rId364" ref="K222"/>
-    <hyperlink r:id="rId365" ref="AJ222"/>
-    <hyperlink r:id="rId366" ref="K224"/>
-    <hyperlink r:id="rId367" ref="AJ224"/>
-    <hyperlink r:id="rId368" ref="K225"/>
-    <hyperlink r:id="rId369" ref="AJ225"/>
-    <hyperlink r:id="rId370" ref="K226"/>
-    <hyperlink r:id="rId371" ref="K227"/>
-    <hyperlink r:id="rId372" ref="AJ227"/>
-    <hyperlink r:id="rId373" ref="K229"/>
-    <hyperlink r:id="rId374" ref="AJ229"/>
-    <hyperlink r:id="rId375" ref="K231"/>
-    <hyperlink r:id="rId376" ref="AJ231"/>
-    <hyperlink r:id="rId377" ref="K233"/>
-    <hyperlink r:id="rId378" ref="AJ233"/>
-    <hyperlink r:id="rId379" ref="K234"/>
-    <hyperlink r:id="rId380" ref="AJ234"/>
-    <hyperlink r:id="rId381" ref="AT235"/>
-    <hyperlink r:id="rId382" ref="K236"/>
-    <hyperlink r:id="rId383" ref="AJ236"/>
-    <hyperlink r:id="rId384" ref="K237"/>
-    <hyperlink r:id="rId385" ref="AJ237"/>
-    <hyperlink r:id="rId386" ref="K238"/>
-    <hyperlink r:id="rId387" ref="AL238"/>
-    <hyperlink r:id="rId388" ref="K239"/>
-    <hyperlink r:id="rId389" ref="AJ239"/>
-    <hyperlink r:id="rId390" ref="K240"/>
-    <hyperlink r:id="rId391" ref="AJ240"/>
-    <hyperlink r:id="rId392" ref="K243"/>
-    <hyperlink r:id="rId393" ref="K244"/>
-    <hyperlink r:id="rId394" ref="AJ244"/>
-    <hyperlink r:id="rId395" ref="K245"/>
-    <hyperlink r:id="rId396" ref="AJ245"/>
-    <hyperlink r:id="rId397" ref="K247"/>
-    <hyperlink r:id="rId398" ref="AJ247"/>
-    <hyperlink r:id="rId399" ref="K248"/>
-    <hyperlink r:id="rId400" ref="AJ248"/>
-    <hyperlink r:id="rId401" ref="K249"/>
-    <hyperlink r:id="rId402" ref="AJ249"/>
-    <hyperlink r:id="rId403" ref="AJ250"/>
-    <hyperlink r:id="rId404" ref="K253"/>
-    <hyperlink r:id="rId405" ref="AJ253"/>
-    <hyperlink r:id="rId406" ref="K254"/>
-    <hyperlink r:id="rId407" ref="AJ254"/>
-    <hyperlink r:id="rId408" ref="K255"/>
-    <hyperlink r:id="rId409" ref="AJ255"/>
-    <hyperlink r:id="rId410" ref="K256"/>
-    <hyperlink r:id="rId411" ref="AJ256"/>
-    <hyperlink r:id="rId412" ref="K257"/>
-    <hyperlink r:id="rId413" ref="AJ257"/>
-    <hyperlink r:id="rId414" ref="K258"/>
-    <hyperlink r:id="rId415" ref="Y258"/>
-    <hyperlink r:id="rId416" ref="AJ258"/>
-    <hyperlink r:id="rId417" ref="K259"/>
-    <hyperlink r:id="rId418" ref="AJ259"/>
-    <hyperlink r:id="rId419" ref="K260"/>
-    <hyperlink r:id="rId420" ref="AJ260"/>
-    <hyperlink r:id="rId421" ref="K261"/>
-    <hyperlink r:id="rId422" ref="AJ261"/>
-    <hyperlink r:id="rId423" ref="K262"/>
-    <hyperlink r:id="rId424" ref="AJ262"/>
-    <hyperlink r:id="rId425" ref="K263"/>
-    <hyperlink r:id="rId426" ref="AJ263"/>
-    <hyperlink r:id="rId427" ref="K265"/>
-    <hyperlink r:id="rId428" ref="AJ265"/>
-    <hyperlink r:id="rId429" location="v=onepage&amp;q=%22Deutschen%20Evangelischen%20Synode%20von%20S%C3%BCdwestafrika%22&amp;f=false" ref="AT265"/>
-    <hyperlink r:id="rId430" ref="K266"/>
-    <hyperlink r:id="rId431" ref="AK266"/>
-    <hyperlink r:id="rId432" ref="K267"/>
-    <hyperlink r:id="rId433" ref="AJ267"/>
-    <hyperlink r:id="rId434" ref="AT268"/>
-    <hyperlink r:id="rId435" ref="K269"/>
-    <hyperlink r:id="rId436" ref="AJ269"/>
-    <hyperlink r:id="rId437" ref="K270"/>
-    <hyperlink r:id="rId438" ref="AJ270"/>
-    <hyperlink r:id="rId439" ref="K271"/>
-    <hyperlink r:id="rId440" ref="AJ271"/>
-    <hyperlink r:id="rId441" ref="K272"/>
-    <hyperlink r:id="rId442" ref="AJ272"/>
-    <hyperlink r:id="rId443" ref="K273"/>
-    <hyperlink r:id="rId444" ref="AJ273"/>
-    <hyperlink r:id="rId445" ref="K274"/>
-    <hyperlink r:id="rId446" ref="AJ274"/>
-    <hyperlink r:id="rId447" ref="AJ275"/>
-    <hyperlink r:id="rId448" ref="K276"/>
-    <hyperlink r:id="rId449" ref="AJ276"/>
-    <hyperlink r:id="rId450" ref="K277"/>
-    <hyperlink r:id="rId451" ref="AJ277"/>
-    <hyperlink r:id="rId452" ref="K278"/>
-    <hyperlink r:id="rId453" ref="AJ278"/>
-    <hyperlink r:id="rId454" ref="K279"/>
-    <hyperlink r:id="rId455" ref="Y279"/>
-    <hyperlink r:id="rId456" ref="AA279"/>
-    <hyperlink r:id="rId457" ref="K280"/>
-    <hyperlink r:id="rId458" ref="AJ280"/>
-    <hyperlink r:id="rId459" ref="K281"/>
-    <hyperlink r:id="rId460" ref="AJ281"/>
-    <hyperlink r:id="rId461" ref="AT281"/>
-    <hyperlink r:id="rId462" ref="K282"/>
-    <hyperlink r:id="rId463" ref="AJ282"/>
-    <hyperlink r:id="rId464" ref="K283"/>
-    <hyperlink r:id="rId465" ref="AJ283"/>
-    <hyperlink r:id="rId466" ref="K284"/>
-    <hyperlink r:id="rId467" ref="AJ284"/>
-    <hyperlink r:id="rId468" ref="K285"/>
-    <hyperlink r:id="rId469" ref="AJ285"/>
-    <hyperlink r:id="rId470" ref="K286"/>
-    <hyperlink r:id="rId471" ref="AA286"/>
-    <hyperlink r:id="rId472" ref="AC286"/>
-    <hyperlink r:id="rId473" ref="AJ286"/>
-    <hyperlink r:id="rId474" ref="AK286"/>
-    <hyperlink r:id="rId475" ref="K289"/>
-    <hyperlink r:id="rId476" ref="AJ289"/>
-    <hyperlink r:id="rId477" ref="K290"/>
-    <hyperlink r:id="rId478" ref="AJ290"/>
-    <hyperlink r:id="rId479" ref="K291"/>
-    <hyperlink r:id="rId480" ref="K292"/>
-    <hyperlink r:id="rId481" ref="AJ292"/>
-    <hyperlink r:id="rId482" ref="K293"/>
-    <hyperlink r:id="rId483" ref="AJ293"/>
-    <hyperlink r:id="rId484" ref="K294"/>
-    <hyperlink r:id="rId485" ref="K295"/>
-    <hyperlink r:id="rId486" ref="Y295"/>
-    <hyperlink r:id="rId487" ref="AK295"/>
-    <hyperlink r:id="rId488" ref="K296"/>
-    <hyperlink r:id="rId489" ref="Y296"/>
-    <hyperlink r:id="rId490" ref="K297"/>
-    <hyperlink r:id="rId491" ref="AJ297"/>
-    <hyperlink r:id="rId492" ref="K298"/>
-    <hyperlink r:id="rId493" ref="AK298"/>
-    <hyperlink r:id="rId494" ref="K299"/>
-    <hyperlink r:id="rId495" ref="AJ299"/>
-    <hyperlink r:id="rId496" ref="K300"/>
-    <hyperlink r:id="rId497" ref="AJ300"/>
-    <hyperlink r:id="rId498" ref="K301"/>
-    <hyperlink r:id="rId499" ref="AJ301"/>
-    <hyperlink r:id="rId500" ref="K302"/>
-    <hyperlink r:id="rId501" ref="K303"/>
-    <hyperlink r:id="rId502" ref="AJ303"/>
-    <hyperlink r:id="rId503" ref="K304"/>
-    <hyperlink r:id="rId504" ref="AL304"/>
-    <hyperlink r:id="rId505" ref="K306"/>
-    <hyperlink r:id="rId506" ref="AJ306"/>
-    <hyperlink r:id="rId507" ref="K307"/>
-    <hyperlink r:id="rId508" ref="Y307"/>
-    <hyperlink r:id="rId509" ref="AJ307"/>
-    <hyperlink r:id="rId510" ref="K308"/>
-    <hyperlink r:id="rId511" ref="AJ308"/>
-    <hyperlink r:id="rId512" ref="K309"/>
-    <hyperlink r:id="rId513" ref="AJ309"/>
-    <hyperlink r:id="rId514" ref="K310"/>
-    <hyperlink r:id="rId515" ref="AJ310"/>
-    <hyperlink r:id="rId516" ref="AL311"/>
-    <hyperlink r:id="rId517" ref="K312"/>
-    <hyperlink r:id="rId518" ref="AL312"/>
-    <hyperlink r:id="rId519" ref="K313"/>
-    <hyperlink r:id="rId520" ref="AJ313"/>
-    <hyperlink r:id="rId521" ref="K314"/>
-    <hyperlink r:id="rId522" ref="AJ314"/>
-    <hyperlink r:id="rId523" ref="K315"/>
-    <hyperlink r:id="rId524" ref="AJ315"/>
-    <hyperlink r:id="rId525" ref="K316"/>
-    <hyperlink r:id="rId526" ref="AL316"/>
-    <hyperlink r:id="rId527" ref="K317"/>
-    <hyperlink r:id="rId528" ref="AJ317"/>
-    <hyperlink r:id="rId529" ref="K318"/>
-    <hyperlink r:id="rId530" ref="AJ318"/>
-    <hyperlink r:id="rId531" ref="K319"/>
-    <hyperlink r:id="rId532" ref="AJ319"/>
-    <hyperlink r:id="rId533" ref="K320"/>
-    <hyperlink r:id="rId534" ref="AJ320"/>
-    <hyperlink r:id="rId535" ref="K323"/>
-    <hyperlink r:id="rId536" ref="AJ323"/>
-    <hyperlink r:id="rId537" ref="K324"/>
-    <hyperlink r:id="rId538" ref="AJ324"/>
-    <hyperlink r:id="rId539" ref="K325"/>
-    <hyperlink r:id="rId540" ref="AJ325"/>
-    <hyperlink r:id="rId541" ref="K326"/>
-    <hyperlink r:id="rId542" ref="AJ326"/>
-    <hyperlink r:id="rId543" ref="K327"/>
-    <hyperlink r:id="rId544" ref="AJ327"/>
-    <hyperlink r:id="rId545" ref="K329"/>
-    <hyperlink r:id="rId546" ref="AJ329"/>
-    <hyperlink r:id="rId547" ref="K330"/>
-    <hyperlink r:id="rId548" ref="AJ330"/>
-    <hyperlink r:id="rId549" ref="K331"/>
-    <hyperlink r:id="rId550" ref="AJ331"/>
-    <hyperlink r:id="rId551" ref="K332"/>
-    <hyperlink r:id="rId552" ref="Y332"/>
-    <hyperlink r:id="rId553" ref="AJ332"/>
-    <hyperlink r:id="rId554" ref="K333"/>
-    <hyperlink r:id="rId555" ref="AJ333"/>
-    <hyperlink r:id="rId556" ref="K334"/>
-    <hyperlink r:id="rId557" ref="AJ334"/>
-    <hyperlink r:id="rId558" ref="K335"/>
-    <hyperlink r:id="rId559" ref="AJ335"/>
-    <hyperlink r:id="rId560" ref="K336"/>
-    <hyperlink r:id="rId561" ref="AJ336"/>
-    <hyperlink r:id="rId562" ref="AJ338"/>
-    <hyperlink r:id="rId563" ref="K340"/>
-    <hyperlink r:id="rId564" ref="K341"/>
-    <hyperlink r:id="rId565" ref="K345"/>
-    <hyperlink r:id="rId566" ref="K346"/>
-    <hyperlink r:id="rId567" ref="AJ346"/>
-    <hyperlink r:id="rId568" ref="K347"/>
-    <hyperlink r:id="rId569" ref="AJ347"/>
-    <hyperlink r:id="rId570" ref="K348"/>
-    <hyperlink r:id="rId571" ref="AJ348"/>
-    <hyperlink r:id="rId572" ref="AJ349"/>
-    <hyperlink r:id="rId573" ref="K350"/>
-    <hyperlink r:id="rId574" ref="AJ350"/>
-    <hyperlink r:id="rId575" ref="K351"/>
-    <hyperlink r:id="rId576" ref="AJ351"/>
-    <hyperlink r:id="rId577" ref="K352"/>
-    <hyperlink r:id="rId578" ref="AK352"/>
-    <hyperlink r:id="rId579" ref="K353"/>
-    <hyperlink r:id="rId580" ref="AJ353"/>
-    <hyperlink r:id="rId581" ref="K354"/>
-    <hyperlink r:id="rId582" ref="AJ354"/>
-    <hyperlink r:id="rId583" ref="K355"/>
-    <hyperlink r:id="rId584" ref="Y355"/>
-    <hyperlink r:id="rId585" ref="AJ355"/>
-    <hyperlink r:id="rId586" ref="K356"/>
-    <hyperlink r:id="rId587" ref="AJ356"/>
-    <hyperlink r:id="rId588" ref="K357"/>
-    <hyperlink r:id="rId589" ref="AJ357"/>
-    <hyperlink r:id="rId590" ref="K358"/>
-    <hyperlink r:id="rId591" ref="AJ358"/>
-    <hyperlink r:id="rId592" ref="K359"/>
-    <hyperlink r:id="rId593" ref="Y359"/>
-    <hyperlink r:id="rId594" ref="AJ359"/>
-    <hyperlink r:id="rId595" ref="K362"/>
-    <hyperlink r:id="rId596" ref="AJ362"/>
-    <hyperlink r:id="rId597" location="v=onepage&amp;q&amp;f=false" ref="AT362"/>
-    <hyperlink r:id="rId598" ref="K363"/>
-    <hyperlink r:id="rId599" ref="AK363"/>
-    <hyperlink r:id="rId600" location="v=onepage&amp;q&amp;f=false" ref="AT363"/>
-    <hyperlink r:id="rId601" ref="K364"/>
-    <hyperlink r:id="rId602" ref="Y364"/>
-    <hyperlink r:id="rId603" ref="AJ364"/>
-    <hyperlink r:id="rId604" ref="K365"/>
-    <hyperlink r:id="rId605" ref="AJ365"/>
-    <hyperlink r:id="rId606" ref="K366"/>
-    <hyperlink r:id="rId607" ref="AJ366"/>
-    <hyperlink r:id="rId608" ref="K367"/>
-    <hyperlink r:id="rId609" ref="AJ367"/>
-    <hyperlink r:id="rId610" ref="AT367"/>
-    <hyperlink r:id="rId611" ref="K368"/>
-    <hyperlink r:id="rId612" ref="AJ368"/>
-    <hyperlink r:id="rId613" ref="K369"/>
-    <hyperlink r:id="rId614" ref="Y369"/>
-    <hyperlink r:id="rId615" ref="AJ369"/>
-    <hyperlink r:id="rId616" ref="K370"/>
-    <hyperlink r:id="rId617" ref="AJ370"/>
-    <hyperlink r:id="rId618" ref="K371"/>
-    <hyperlink r:id="rId619" ref="AJ371"/>
-    <hyperlink r:id="rId620" ref="K372"/>
-    <hyperlink r:id="rId621" ref="AJ372"/>
-    <hyperlink r:id="rId622" ref="K373"/>
-    <hyperlink r:id="rId623" ref="AJ373"/>
-    <hyperlink r:id="rId624" ref="K374"/>
-    <hyperlink r:id="rId625" ref="AJ374"/>
-    <hyperlink r:id="rId626" ref="K375"/>
-    <hyperlink r:id="rId627" ref="AJ375"/>
-    <hyperlink r:id="rId628" ref="K376"/>
-    <hyperlink r:id="rId629" ref="AJ376"/>
-    <hyperlink r:id="rId630" ref="K377"/>
-    <hyperlink r:id="rId631" ref="AJ377"/>
-    <hyperlink r:id="rId632" ref="K378"/>
-    <hyperlink r:id="rId633" ref="AJ378"/>
-    <hyperlink r:id="rId634" ref="K379"/>
-    <hyperlink r:id="rId635" ref="AJ379"/>
-    <hyperlink r:id="rId636" ref="K380"/>
-    <hyperlink r:id="rId637" ref="AJ380"/>
-    <hyperlink r:id="rId638" ref="K381"/>
-    <hyperlink r:id="rId639" ref="AJ381"/>
-    <hyperlink r:id="rId640" ref="K382"/>
-    <hyperlink r:id="rId641" ref="AJ382"/>
-    <hyperlink r:id="rId642" ref="K383"/>
-    <hyperlink r:id="rId643" ref="AJ383"/>
-    <hyperlink r:id="rId644" ref="K384"/>
-    <hyperlink r:id="rId645" ref="AJ384"/>
-    <hyperlink r:id="rId646" ref="K385"/>
-    <hyperlink r:id="rId647" ref="AJ385"/>
-    <hyperlink r:id="rId648" ref="K386"/>
-    <hyperlink r:id="rId649" ref="Y386"/>
-    <hyperlink r:id="rId650" ref="AA386"/>
-    <hyperlink r:id="rId651" ref="AJ386"/>
-    <hyperlink r:id="rId652" ref="K387"/>
-    <hyperlink r:id="rId653" ref="AJ387"/>
-    <hyperlink r:id="rId654" ref="K388"/>
-    <hyperlink r:id="rId655" ref="AJ388"/>
-    <hyperlink r:id="rId656" ref="K389"/>
-    <hyperlink r:id="rId657" ref="AJ389"/>
-    <hyperlink r:id="rId658" ref="K390"/>
-    <hyperlink r:id="rId659" ref="AJ390"/>
-    <hyperlink r:id="rId660" ref="K391"/>
-    <hyperlink r:id="rId661" ref="AJ391"/>
-    <hyperlink r:id="rId662" ref="K392"/>
-    <hyperlink r:id="rId663" ref="AJ392"/>
-    <hyperlink r:id="rId664" ref="K393"/>
-    <hyperlink r:id="rId665" ref="AJ393"/>
-    <hyperlink r:id="rId666" ref="K394"/>
-    <hyperlink r:id="rId667" ref="AJ394"/>
-    <hyperlink r:id="rId668" ref="K395"/>
-    <hyperlink r:id="rId669" ref="AJ395"/>
-    <hyperlink r:id="rId670" ref="K396"/>
-    <hyperlink r:id="rId671" ref="AJ396"/>
-    <hyperlink r:id="rId672" ref="K397"/>
-    <hyperlink r:id="rId673" ref="AJ397"/>
-    <hyperlink r:id="rId674" ref="K398"/>
-    <hyperlink r:id="rId675" ref="AJ398"/>
-    <hyperlink r:id="rId676" ref="K399"/>
-    <hyperlink r:id="rId677" ref="AJ399"/>
-    <hyperlink r:id="rId678" ref="K400"/>
-    <hyperlink r:id="rId679" ref="AJ400"/>
-    <hyperlink r:id="rId680" ref="K401"/>
-    <hyperlink r:id="rId681" ref="AJ401"/>
-    <hyperlink r:id="rId682" ref="K402"/>
-    <hyperlink r:id="rId683" ref="AJ402"/>
-    <hyperlink r:id="rId684" ref="K403"/>
-    <hyperlink r:id="rId685" ref="AJ403"/>
-    <hyperlink r:id="rId686" ref="K404"/>
-    <hyperlink r:id="rId687" ref="AJ404"/>
-    <hyperlink r:id="rId688" ref="K405"/>
-    <hyperlink r:id="rId689" ref="AJ405"/>
-    <hyperlink r:id="rId690" ref="K410"/>
-    <hyperlink r:id="rId691" ref="AJ410"/>
-    <hyperlink r:id="rId692" ref="K411"/>
-    <hyperlink r:id="rId693" ref="AJ411"/>
-    <hyperlink r:id="rId694" ref="K412"/>
-    <hyperlink r:id="rId695" ref="K413"/>
-    <hyperlink r:id="rId696" ref="AJ413"/>
-    <hyperlink r:id="rId697" ref="AJ414"/>
-    <hyperlink r:id="rId698" ref="AK415"/>
-    <hyperlink r:id="rId699" ref="AL415"/>
-    <hyperlink r:id="rId700" ref="K417"/>
-    <hyperlink r:id="rId701" ref="AJ417"/>
-    <hyperlink r:id="rId702" ref="K418"/>
-    <hyperlink r:id="rId703" ref="AJ418"/>
-    <hyperlink r:id="rId704" ref="K419"/>
-    <hyperlink r:id="rId705" ref="AJ419"/>
-    <hyperlink r:id="rId706" ref="K420"/>
-    <hyperlink r:id="rId707" ref="AJ420"/>
-    <hyperlink r:id="rId708" ref="K423"/>
-    <hyperlink r:id="rId709" ref="AJ423"/>
-    <hyperlink r:id="rId710" ref="AK423"/>
-    <hyperlink r:id="rId711" ref="K424"/>
-    <hyperlink r:id="rId712" ref="AJ424"/>
-    <hyperlink r:id="rId713" ref="AL425"/>
-    <hyperlink r:id="rId714" ref="K426"/>
-    <hyperlink r:id="rId715" ref="AJ426"/>
-    <hyperlink r:id="rId716" ref="K427"/>
-    <hyperlink r:id="rId717" ref="AG427"/>
-    <hyperlink r:id="rId718" ref="AJ427"/>
-    <hyperlink r:id="rId719" ref="K428"/>
-    <hyperlink r:id="rId720" ref="AJ428"/>
-    <hyperlink r:id="rId721" ref="K429"/>
-    <hyperlink r:id="rId722" ref="AJ429"/>
-    <hyperlink r:id="rId723" ref="K430"/>
-    <hyperlink r:id="rId724" ref="AJ430"/>
-    <hyperlink r:id="rId725" ref="K431"/>
-    <hyperlink r:id="rId726" ref="AJ431"/>
-    <hyperlink r:id="rId727" ref="K432"/>
-    <hyperlink r:id="rId728" ref="AJ432"/>
-    <hyperlink r:id="rId729" ref="K433"/>
-    <hyperlink r:id="rId730" ref="AJ433"/>
-    <hyperlink r:id="rId731" ref="K434"/>
-    <hyperlink r:id="rId732" ref="AJ434"/>
-    <hyperlink r:id="rId733" ref="K435"/>
-    <hyperlink r:id="rId734" ref="K436"/>
-    <hyperlink r:id="rId735" ref="AJ436"/>
-    <hyperlink r:id="rId736" ref="K437"/>
-    <hyperlink r:id="rId737" ref="AJ437"/>
-    <hyperlink r:id="rId738" ref="K438"/>
-    <hyperlink r:id="rId739" ref="AJ438"/>
-    <hyperlink r:id="rId740" ref="AJ439"/>
-    <hyperlink r:id="rId741" ref="K440"/>
-    <hyperlink r:id="rId742" ref="AJ440"/>
-    <hyperlink r:id="rId743" ref="K441"/>
-    <hyperlink r:id="rId744" ref="AJ441"/>
-    <hyperlink r:id="rId745" ref="K442"/>
-    <hyperlink r:id="rId746" ref="AJ442"/>
-    <hyperlink r:id="rId747" ref="K443"/>
-    <hyperlink r:id="rId748" ref="AJ443"/>
-    <hyperlink r:id="rId749" ref="K445"/>
-    <hyperlink r:id="rId750" ref="AJ445"/>
-    <hyperlink r:id="rId751" ref="K446"/>
-    <hyperlink r:id="rId752" ref="K447"/>
-    <hyperlink r:id="rId753" ref="AA447"/>
-    <hyperlink r:id="rId754" ref="K448"/>
-    <hyperlink r:id="rId755" ref="AJ448"/>
-    <hyperlink r:id="rId756" ref="K449"/>
-    <hyperlink r:id="rId757" ref="AJ449"/>
-    <hyperlink r:id="rId758" ref="K450"/>
-    <hyperlink r:id="rId759" ref="AG450"/>
-    <hyperlink r:id="rId760" ref="AJ450"/>
-    <hyperlink r:id="rId761" ref="K451"/>
-    <hyperlink r:id="rId762" ref="AG451"/>
-    <hyperlink r:id="rId763" ref="AJ451"/>
-    <hyperlink r:id="rId764" ref="K452"/>
-    <hyperlink r:id="rId765" ref="AJ452"/>
-    <hyperlink r:id="rId766" ref="K453"/>
-    <hyperlink r:id="rId767" ref="AJ453"/>
-    <hyperlink r:id="rId768" ref="K454"/>
-    <hyperlink r:id="rId769" ref="AJ454"/>
-    <hyperlink r:id="rId770" ref="K455"/>
-    <hyperlink r:id="rId771" ref="AJ455"/>
-    <hyperlink r:id="rId772" ref="K456"/>
-    <hyperlink r:id="rId773" ref="Y456"/>
-    <hyperlink r:id="rId774" ref="AJ456"/>
-    <hyperlink r:id="rId775" ref="K457"/>
-    <hyperlink r:id="rId776" ref="AJ457"/>
-    <hyperlink r:id="rId777" ref="K458"/>
-    <hyperlink r:id="rId778" ref="AJ458"/>
-    <hyperlink r:id="rId779" ref="K459"/>
-    <hyperlink r:id="rId780" ref="AJ459"/>
-    <hyperlink r:id="rId781" ref="K461"/>
-    <hyperlink r:id="rId782" ref="AG461"/>
-    <hyperlink r:id="rId783" ref="AJ461"/>
-    <hyperlink r:id="rId784" ref="K462"/>
-    <hyperlink r:id="rId785" ref="AJ462"/>
-    <hyperlink r:id="rId786" ref="AT462"/>
-    <hyperlink r:id="rId787" ref="K463"/>
-    <hyperlink r:id="rId788" ref="AJ463"/>
-    <hyperlink r:id="rId789" ref="K464"/>
-    <hyperlink r:id="rId790" ref="AJ464"/>
-    <hyperlink r:id="rId791" ref="K466"/>
-    <hyperlink r:id="rId792" ref="K468"/>
-    <hyperlink r:id="rId793" ref="AJ468"/>
-    <hyperlink r:id="rId794" ref="K470"/>
-    <hyperlink r:id="rId795" ref="AJ470"/>
-    <hyperlink r:id="rId796" ref="K471"/>
-    <hyperlink r:id="rId797" ref="Y471"/>
-    <hyperlink r:id="rId798" ref="AJ471"/>
-    <hyperlink r:id="rId799" ref="K472"/>
-    <hyperlink r:id="rId800" ref="AJ472"/>
-    <hyperlink r:id="rId801" ref="K473"/>
-    <hyperlink r:id="rId802" ref="AJ473"/>
-    <hyperlink r:id="rId803" ref="K474"/>
-    <hyperlink r:id="rId804" ref="AJ474"/>
-    <hyperlink r:id="rId805" ref="K475"/>
-    <hyperlink r:id="rId806" ref="AJ475"/>
-    <hyperlink r:id="rId807" ref="AK476"/>
-    <hyperlink r:id="rId808" ref="K477"/>
-    <hyperlink r:id="rId809" ref="K478"/>
-    <hyperlink r:id="rId810" ref="AJ478"/>
-    <hyperlink r:id="rId811" ref="K479"/>
-    <hyperlink r:id="rId812" ref="AJ479"/>
-    <hyperlink r:id="rId813" ref="K480"/>
-    <hyperlink r:id="rId814" ref="AJ480"/>
-    <hyperlink r:id="rId815" ref="K481"/>
-    <hyperlink r:id="rId816" ref="AJ481"/>
-    <hyperlink r:id="rId817" ref="K482"/>
-    <hyperlink r:id="rId818" ref="AK482"/>
-    <hyperlink r:id="rId819" ref="K483"/>
-    <hyperlink r:id="rId820" ref="AJ483"/>
-    <hyperlink r:id="rId821" ref="K484"/>
-    <hyperlink r:id="rId822" ref="AJ484"/>
-    <hyperlink r:id="rId823" ref="K485"/>
-    <hyperlink r:id="rId824" ref="AJ485"/>
-    <hyperlink r:id="rId825" ref="K486"/>
-    <hyperlink r:id="rId826" ref="AJ486"/>
-    <hyperlink r:id="rId827" ref="K487"/>
-    <hyperlink r:id="rId828" ref="K488"/>
-    <hyperlink r:id="rId829" ref="AJ488"/>
-    <hyperlink r:id="rId830" ref="K489"/>
-    <hyperlink r:id="rId831" ref="AJ489"/>
-    <hyperlink r:id="rId832" ref="K490"/>
-    <hyperlink r:id="rId833" ref="AJ490"/>
-    <hyperlink r:id="rId834" ref="AT492"/>
-    <hyperlink r:id="rId835" ref="K493"/>
-    <hyperlink r:id="rId836" ref="AJ493"/>
-    <hyperlink r:id="rId837" ref="K494"/>
-    <hyperlink r:id="rId838" ref="AJ494"/>
-    <hyperlink r:id="rId839" ref="K495"/>
-    <hyperlink r:id="rId840" ref="Y495"/>
-    <hyperlink r:id="rId841" ref="AJ495"/>
-    <hyperlink r:id="rId842" ref="K496"/>
-    <hyperlink r:id="rId843" ref="AJ496"/>
-    <hyperlink r:id="rId844" ref="K497"/>
-    <hyperlink r:id="rId845" ref="AJ497"/>
-    <hyperlink r:id="rId846" ref="K498"/>
-    <hyperlink r:id="rId847" ref="AJ498"/>
-    <hyperlink r:id="rId848" ref="K499"/>
-    <hyperlink r:id="rId849" ref="AJ499"/>
-    <hyperlink r:id="rId850" ref="K500"/>
-    <hyperlink r:id="rId851" ref="AJ500"/>
-    <hyperlink r:id="rId852" ref="K501"/>
-    <hyperlink r:id="rId853" ref="AJ501"/>
-    <hyperlink r:id="rId854" ref="AT501"/>
-    <hyperlink r:id="rId855" ref="K502"/>
-    <hyperlink r:id="rId856" ref="AJ502"/>
-    <hyperlink r:id="rId857" ref="K503"/>
-    <hyperlink r:id="rId858" ref="AJ503"/>
-    <hyperlink r:id="rId859" ref="K504"/>
-    <hyperlink r:id="rId860" ref="AJ504"/>
-    <hyperlink r:id="rId861" ref="K505"/>
-    <hyperlink r:id="rId862" ref="AJ505"/>
-    <hyperlink r:id="rId863" ref="K506"/>
-    <hyperlink r:id="rId864" ref="Y506"/>
-    <hyperlink r:id="rId865" ref="AJ506"/>
-    <hyperlink r:id="rId866" ref="K507"/>
-    <hyperlink r:id="rId867" ref="Y507"/>
-    <hyperlink r:id="rId868" ref="AJ507"/>
-    <hyperlink r:id="rId869" ref="K508"/>
-    <hyperlink r:id="rId870" ref="AJ508"/>
-    <hyperlink r:id="rId871" ref="K509"/>
-    <hyperlink r:id="rId872" ref="AJ509"/>
-    <hyperlink r:id="rId873" ref="K510"/>
-    <hyperlink r:id="rId874" ref="AJ510"/>
-    <hyperlink r:id="rId875" ref="K511"/>
-    <hyperlink r:id="rId876" ref="AJ511"/>
-    <hyperlink r:id="rId877" ref="AT511"/>
-    <hyperlink r:id="rId878" ref="K512"/>
-    <hyperlink r:id="rId879" ref="AT512"/>
-    <hyperlink r:id="rId880" ref="K513"/>
-    <hyperlink r:id="rId881" ref="AJ513"/>
-    <hyperlink r:id="rId882" ref="AT513"/>
-    <hyperlink r:id="rId883" ref="AJ514"/>
-    <hyperlink r:id="rId884" ref="K515"/>
-    <hyperlink r:id="rId885" ref="AJ515"/>
-    <hyperlink r:id="rId886" ref="K517"/>
-    <hyperlink r:id="rId887" ref="AJ517"/>
-    <hyperlink r:id="rId888" ref="K518"/>
-    <hyperlink r:id="rId889" ref="AJ518"/>
-    <hyperlink r:id="rId890" ref="K520"/>
-    <hyperlink r:id="rId891" ref="AJ520"/>
-    <hyperlink r:id="rId892" ref="K521"/>
-    <hyperlink r:id="rId893" ref="AJ521"/>
-    <hyperlink r:id="rId894" ref="AT524"/>
-    <hyperlink r:id="rId895" ref="K525"/>
-    <hyperlink r:id="rId896" ref="AJ525"/>
-    <hyperlink r:id="rId897" ref="K526"/>
-    <hyperlink r:id="rId898" ref="AJ526"/>
-    <hyperlink r:id="rId899" ref="K527"/>
-    <hyperlink r:id="rId900" ref="AJ527"/>
-    <hyperlink r:id="rId901" ref="K528"/>
-    <hyperlink r:id="rId902" ref="AJ528"/>
-    <hyperlink r:id="rId903" ref="K529"/>
-    <hyperlink r:id="rId904" ref="AJ529"/>
-    <hyperlink r:id="rId905" ref="K530"/>
-    <hyperlink r:id="rId906" ref="AJ530"/>
-    <hyperlink r:id="rId907" ref="K531"/>
-    <hyperlink r:id="rId908" ref="AJ531"/>
-    <hyperlink r:id="rId909" ref="K532"/>
-    <hyperlink r:id="rId910" ref="AK532"/>
-    <hyperlink r:id="rId911" ref="K533"/>
-    <hyperlink r:id="rId912" ref="AJ533"/>
-    <hyperlink r:id="rId913" ref="K534"/>
-    <hyperlink r:id="rId914" ref="AJ534"/>
-    <hyperlink r:id="rId915" ref="K535"/>
-    <hyperlink r:id="rId916" ref="AJ535"/>
-    <hyperlink r:id="rId917" ref="K536"/>
-    <hyperlink r:id="rId918" ref="AJ536"/>
-    <hyperlink r:id="rId919" ref="K537"/>
-    <hyperlink r:id="rId920" ref="AJ537"/>
-    <hyperlink r:id="rId921" ref="K538"/>
-    <hyperlink r:id="rId922" ref="AJ538"/>
-    <hyperlink r:id="rId923" ref="AT538"/>
-    <hyperlink r:id="rId924" ref="K539"/>
-    <hyperlink r:id="rId925" ref="Y539"/>
-    <hyperlink r:id="rId926" ref="AJ539"/>
-    <hyperlink r:id="rId927" ref="K540"/>
-    <hyperlink r:id="rId928" ref="AJ540"/>
+    <hyperlink r:id="rId350" ref="AJ216"/>
+    <hyperlink r:id="rId351" ref="AM216"/>
+    <hyperlink r:id="rId352" location="v=onepage&amp;q&amp;f=false" ref="AT216"/>
+    <hyperlink r:id="rId353" ref="K217"/>
+    <hyperlink r:id="rId354" ref="AK217"/>
+    <hyperlink r:id="rId355" ref="K218"/>
+    <hyperlink r:id="rId356" ref="AJ218"/>
+    <hyperlink r:id="rId357" ref="K219"/>
+    <hyperlink r:id="rId358" ref="AJ219"/>
+    <hyperlink r:id="rId359" ref="K220"/>
+    <hyperlink r:id="rId360" ref="AJ220"/>
+    <hyperlink r:id="rId361" ref="K221"/>
+    <hyperlink r:id="rId362" ref="AJ221"/>
+    <hyperlink r:id="rId363" ref="K222"/>
+    <hyperlink r:id="rId364" ref="AJ222"/>
+    <hyperlink r:id="rId365" ref="K224"/>
+    <hyperlink r:id="rId366" ref="AJ224"/>
+    <hyperlink r:id="rId367" ref="K225"/>
+    <hyperlink r:id="rId368" ref="AJ225"/>
+    <hyperlink r:id="rId369" ref="K226"/>
+    <hyperlink r:id="rId370" ref="K227"/>
+    <hyperlink r:id="rId371" ref="AJ227"/>
+    <hyperlink r:id="rId372" ref="K229"/>
+    <hyperlink r:id="rId373" ref="AJ229"/>
+    <hyperlink r:id="rId374" ref="K231"/>
+    <hyperlink r:id="rId375" ref="AJ231"/>
+    <hyperlink r:id="rId376" ref="K233"/>
+    <hyperlink r:id="rId377" ref="AJ233"/>
+    <hyperlink r:id="rId378" ref="K234"/>
+    <hyperlink r:id="rId379" ref="AJ234"/>
+    <hyperlink r:id="rId380" ref="AT235"/>
+    <hyperlink r:id="rId381" ref="K236"/>
+    <hyperlink r:id="rId382" ref="AJ236"/>
+    <hyperlink r:id="rId383" ref="K237"/>
+    <hyperlink r:id="rId384" ref="AJ237"/>
+    <hyperlink r:id="rId385" ref="K238"/>
+    <hyperlink r:id="rId386" ref="AL238"/>
+    <hyperlink r:id="rId387" ref="K239"/>
+    <hyperlink r:id="rId388" ref="AJ239"/>
+    <hyperlink r:id="rId389" ref="K240"/>
+    <hyperlink r:id="rId390" ref="AJ240"/>
+    <hyperlink r:id="rId391" ref="K243"/>
+    <hyperlink r:id="rId392" ref="K244"/>
+    <hyperlink r:id="rId393" ref="AJ244"/>
+    <hyperlink r:id="rId394" ref="K245"/>
+    <hyperlink r:id="rId395" ref="AJ245"/>
+    <hyperlink r:id="rId396" ref="K247"/>
+    <hyperlink r:id="rId397" ref="AJ247"/>
+    <hyperlink r:id="rId398" ref="K248"/>
+    <hyperlink r:id="rId399" ref="AJ248"/>
+    <hyperlink r:id="rId400" ref="K249"/>
+    <hyperlink r:id="rId401" ref="AJ249"/>
+    <hyperlink r:id="rId402" ref="AJ250"/>
+    <hyperlink r:id="rId403" ref="K253"/>
+    <hyperlink r:id="rId404" ref="AJ253"/>
+    <hyperlink r:id="rId405" ref="K254"/>
+    <hyperlink r:id="rId406" ref="AJ254"/>
+    <hyperlink r:id="rId407" ref="K255"/>
+    <hyperlink r:id="rId408" ref="AJ255"/>
+    <hyperlink r:id="rId409" ref="K256"/>
+    <hyperlink r:id="rId410" ref="AJ256"/>
+    <hyperlink r:id="rId411" ref="K257"/>
+    <hyperlink r:id="rId412" ref="AJ257"/>
+    <hyperlink r:id="rId413" ref="K258"/>
+    <hyperlink r:id="rId414" ref="Y258"/>
+    <hyperlink r:id="rId415" ref="AJ258"/>
+    <hyperlink r:id="rId416" ref="K259"/>
+    <hyperlink r:id="rId417" ref="AJ259"/>
+    <hyperlink r:id="rId418" ref="K260"/>
+    <hyperlink r:id="rId419" ref="AJ260"/>
+    <hyperlink r:id="rId420" ref="K261"/>
+    <hyperlink r:id="rId421" ref="AJ261"/>
+    <hyperlink r:id="rId422" ref="K262"/>
+    <hyperlink r:id="rId423" ref="AJ262"/>
+    <hyperlink r:id="rId424" ref="K263"/>
+    <hyperlink r:id="rId425" ref="AJ263"/>
+    <hyperlink r:id="rId426" ref="K265"/>
+    <hyperlink r:id="rId427" ref="AJ265"/>
+    <hyperlink r:id="rId428" location="v=onepage&amp;q=%22Deutschen%20Evangelischen%20Synode%20von%20S%C3%BCdwestafrika%22&amp;f=false" ref="AT265"/>
+    <hyperlink r:id="rId429" ref="K266"/>
+    <hyperlink r:id="rId430" ref="AK266"/>
+    <hyperlink r:id="rId431" ref="K267"/>
+    <hyperlink r:id="rId432" ref="AJ267"/>
+    <hyperlink r:id="rId433" ref="AT268"/>
+    <hyperlink r:id="rId434" ref="K269"/>
+    <hyperlink r:id="rId435" ref="AJ269"/>
+    <hyperlink r:id="rId436" ref="K270"/>
+    <hyperlink r:id="rId437" ref="AJ270"/>
+    <hyperlink r:id="rId438" ref="K271"/>
+    <hyperlink r:id="rId439" ref="AJ271"/>
+    <hyperlink r:id="rId440" ref="K272"/>
+    <hyperlink r:id="rId441" ref="AJ272"/>
+    <hyperlink r:id="rId442" ref="K273"/>
+    <hyperlink r:id="rId443" ref="AJ273"/>
+    <hyperlink r:id="rId444" ref="K274"/>
+    <hyperlink r:id="rId445" ref="AJ274"/>
+    <hyperlink r:id="rId446" ref="AJ275"/>
+    <hyperlink r:id="rId447" ref="K276"/>
+    <hyperlink r:id="rId448" ref="AJ276"/>
+    <hyperlink r:id="rId449" ref="K277"/>
+    <hyperlink r:id="rId450" ref="AJ277"/>
+    <hyperlink r:id="rId451" ref="K278"/>
+    <hyperlink r:id="rId452" ref="AJ278"/>
+    <hyperlink r:id="rId453" ref="K279"/>
+    <hyperlink r:id="rId454" ref="Y279"/>
+    <hyperlink r:id="rId455" ref="AA279"/>
+    <hyperlink r:id="rId456" ref="K280"/>
+    <hyperlink r:id="rId457" ref="AJ280"/>
+    <hyperlink r:id="rId458" ref="K281"/>
+    <hyperlink r:id="rId459" ref="AJ281"/>
+    <hyperlink r:id="rId460" ref="AT281"/>
+    <hyperlink r:id="rId461" ref="K282"/>
+    <hyperlink r:id="rId462" ref="AJ282"/>
+    <hyperlink r:id="rId463" ref="K283"/>
+    <hyperlink r:id="rId464" ref="AJ283"/>
+    <hyperlink r:id="rId465" ref="K284"/>
+    <hyperlink r:id="rId466" ref="AJ284"/>
+    <hyperlink r:id="rId467" ref="K285"/>
+    <hyperlink r:id="rId468" ref="AJ285"/>
+    <hyperlink r:id="rId469" ref="K286"/>
+    <hyperlink r:id="rId470" ref="AA286"/>
+    <hyperlink r:id="rId471" ref="AC286"/>
+    <hyperlink r:id="rId472" ref="AJ286"/>
+    <hyperlink r:id="rId473" ref="AK286"/>
+    <hyperlink r:id="rId474" ref="K289"/>
+    <hyperlink r:id="rId475" ref="AJ289"/>
+    <hyperlink r:id="rId476" ref="K290"/>
+    <hyperlink r:id="rId477" ref="AJ290"/>
+    <hyperlink r:id="rId478" ref="K291"/>
+    <hyperlink r:id="rId479" ref="K292"/>
+    <hyperlink r:id="rId480" ref="AJ292"/>
+    <hyperlink r:id="rId481" ref="K293"/>
+    <hyperlink r:id="rId482" ref="AJ293"/>
+    <hyperlink r:id="rId483" ref="K294"/>
+    <hyperlink r:id="rId484" ref="K295"/>
+    <hyperlink r:id="rId485" ref="Y295"/>
+    <hyperlink r:id="rId486" ref="AK295"/>
+    <hyperlink r:id="rId487" ref="K296"/>
+    <hyperlink r:id="rId488" ref="Y296"/>
+    <hyperlink r:id="rId489" ref="K297"/>
+    <hyperlink r:id="rId490" ref="AJ297"/>
+    <hyperlink r:id="rId491" ref="K298"/>
+    <hyperlink r:id="rId492" ref="AK298"/>
+    <hyperlink r:id="rId493" ref="K299"/>
+    <hyperlink r:id="rId494" ref="AJ299"/>
+    <hyperlink r:id="rId495" ref="K300"/>
+    <hyperlink r:id="rId496" ref="AJ300"/>
+    <hyperlink r:id="rId497" ref="K301"/>
+    <hyperlink r:id="rId498" ref="AJ301"/>
+    <hyperlink r:id="rId499" ref="K302"/>
+    <hyperlink r:id="rId500" ref="K303"/>
+    <hyperlink r:id="rId501" ref="AJ303"/>
+    <hyperlink r:id="rId502" ref="K304"/>
+    <hyperlink r:id="rId503" ref="AL304"/>
+    <hyperlink r:id="rId504" ref="K306"/>
+    <hyperlink r:id="rId505" ref="AJ306"/>
+    <hyperlink r:id="rId506" ref="K307"/>
+    <hyperlink r:id="rId507" ref="Y307"/>
+    <hyperlink r:id="rId508" ref="AJ307"/>
+    <hyperlink r:id="rId509" ref="K308"/>
+    <hyperlink r:id="rId510" ref="AJ308"/>
+    <hyperlink r:id="rId511" ref="K309"/>
+    <hyperlink r:id="rId512" ref="AJ309"/>
+    <hyperlink r:id="rId513" ref="K310"/>
+    <hyperlink r:id="rId514" ref="AJ310"/>
+    <hyperlink r:id="rId515" ref="AL311"/>
+    <hyperlink r:id="rId516" ref="K312"/>
+    <hyperlink r:id="rId517" ref="AL312"/>
+    <hyperlink r:id="rId518" ref="K313"/>
+    <hyperlink r:id="rId519" ref="AJ313"/>
+    <hyperlink r:id="rId520" ref="K314"/>
+    <hyperlink r:id="rId521" ref="AJ314"/>
+    <hyperlink r:id="rId522" ref="K315"/>
+    <hyperlink r:id="rId523" ref="AJ315"/>
+    <hyperlink r:id="rId524" ref="K316"/>
+    <hyperlink r:id="rId525" ref="AL316"/>
+    <hyperlink r:id="rId526" ref="K317"/>
+    <hyperlink r:id="rId527" ref="AJ317"/>
+    <hyperlink r:id="rId528" ref="K318"/>
+    <hyperlink r:id="rId529" ref="AJ318"/>
+    <hyperlink r:id="rId530" ref="K319"/>
+    <hyperlink r:id="rId531" ref="AJ319"/>
+    <hyperlink r:id="rId532" ref="K320"/>
+    <hyperlink r:id="rId533" ref="AJ320"/>
+    <hyperlink r:id="rId534" ref="K323"/>
+    <hyperlink r:id="rId535" ref="AJ323"/>
+    <hyperlink r:id="rId536" ref="K324"/>
+    <hyperlink r:id="rId537" ref="AJ324"/>
+    <hyperlink r:id="rId538" ref="K325"/>
+    <hyperlink r:id="rId539" ref="AJ325"/>
+    <hyperlink r:id="rId540" ref="K326"/>
+    <hyperlink r:id="rId541" ref="AJ326"/>
+    <hyperlink r:id="rId542" ref="K327"/>
+    <hyperlink r:id="rId543" ref="AJ327"/>
+    <hyperlink r:id="rId544" ref="K329"/>
+    <hyperlink r:id="rId545" ref="AJ329"/>
+    <hyperlink r:id="rId546" ref="K330"/>
+    <hyperlink r:id="rId547" ref="AJ330"/>
+    <hyperlink r:id="rId548" ref="K331"/>
+    <hyperlink r:id="rId549" ref="AJ331"/>
+    <hyperlink r:id="rId550" ref="K332"/>
+    <hyperlink r:id="rId551" ref="Y332"/>
+    <hyperlink r:id="rId552" ref="AJ332"/>
+    <hyperlink r:id="rId553" ref="K333"/>
+    <hyperlink r:id="rId554" ref="AJ333"/>
+    <hyperlink r:id="rId555" ref="K334"/>
+    <hyperlink r:id="rId556" ref="AJ334"/>
+    <hyperlink r:id="rId557" ref="K335"/>
+    <hyperlink r:id="rId558" ref="AJ335"/>
+    <hyperlink r:id="rId559" ref="K336"/>
+    <hyperlink r:id="rId560" ref="AJ336"/>
+    <hyperlink r:id="rId561" ref="AJ338"/>
+    <hyperlink r:id="rId562" ref="K340"/>
+    <hyperlink r:id="rId563" ref="K341"/>
+    <hyperlink r:id="rId564" ref="K345"/>
+    <hyperlink r:id="rId565" ref="K346"/>
+    <hyperlink r:id="rId566" ref="AJ346"/>
+    <hyperlink r:id="rId567" ref="K347"/>
+    <hyperlink r:id="rId568" ref="AJ347"/>
+    <hyperlink r:id="rId569" ref="K348"/>
+    <hyperlink r:id="rId570" ref="AJ348"/>
+    <hyperlink r:id="rId571" ref="AJ349"/>
+    <hyperlink r:id="rId572" ref="K350"/>
+    <hyperlink r:id="rId573" ref="AJ350"/>
+    <hyperlink r:id="rId574" ref="K351"/>
+    <hyperlink r:id="rId575" ref="AJ351"/>
+    <hyperlink r:id="rId576" ref="K352"/>
+    <hyperlink r:id="rId577" ref="AK352"/>
+    <hyperlink r:id="rId578" ref="K353"/>
+    <hyperlink r:id="rId579" ref="AJ353"/>
+    <hyperlink r:id="rId580" ref="K354"/>
+    <hyperlink r:id="rId581" ref="AJ354"/>
+    <hyperlink r:id="rId582" ref="K355"/>
+    <hyperlink r:id="rId583" ref="Y355"/>
+    <hyperlink r:id="rId584" ref="AJ355"/>
+    <hyperlink r:id="rId585" ref="K356"/>
+    <hyperlink r:id="rId586" ref="AJ356"/>
+    <hyperlink r:id="rId587" ref="K357"/>
+    <hyperlink r:id="rId588" ref="AJ357"/>
+    <hyperlink r:id="rId589" ref="K358"/>
+    <hyperlink r:id="rId590" ref="AJ358"/>
+    <hyperlink r:id="rId591" ref="K359"/>
+    <hyperlink r:id="rId592" ref="Y359"/>
+    <hyperlink r:id="rId593" ref="AJ359"/>
+    <hyperlink r:id="rId594" ref="K362"/>
+    <hyperlink r:id="rId595" ref="AJ362"/>
+    <hyperlink r:id="rId596" location="v=onepage&amp;q&amp;f=false" ref="AT362"/>
+    <hyperlink r:id="rId597" ref="K363"/>
+    <hyperlink r:id="rId598" ref="AK363"/>
+    <hyperlink r:id="rId599" location="v=onepage&amp;q&amp;f=false" ref="AT363"/>
+    <hyperlink r:id="rId600" ref="K364"/>
+    <hyperlink r:id="rId601" ref="Y364"/>
+    <hyperlink r:id="rId602" ref="AJ364"/>
+    <hyperlink r:id="rId603" ref="K365"/>
+    <hyperlink r:id="rId604" ref="AJ365"/>
+    <hyperlink r:id="rId605" ref="K366"/>
+    <hyperlink r:id="rId606" ref="AJ366"/>
+    <hyperlink r:id="rId607" ref="K367"/>
+    <hyperlink r:id="rId608" ref="AJ367"/>
+    <hyperlink r:id="rId609" ref="AT367"/>
+    <hyperlink r:id="rId610" ref="K368"/>
+    <hyperlink r:id="rId611" ref="AJ368"/>
+    <hyperlink r:id="rId612" ref="K369"/>
+    <hyperlink r:id="rId613" ref="Y369"/>
+    <hyperlink r:id="rId614" ref="AJ369"/>
+    <hyperlink r:id="rId615" ref="K370"/>
+    <hyperlink r:id="rId616" ref="AJ370"/>
+    <hyperlink r:id="rId617" ref="K371"/>
+    <hyperlink r:id="rId618" ref="AJ371"/>
+    <hyperlink r:id="rId619" ref="K372"/>
+    <hyperlink r:id="rId620" ref="AJ372"/>
+    <hyperlink r:id="rId621" ref="K373"/>
+    <hyperlink r:id="rId622" ref="AJ373"/>
+    <hyperlink r:id="rId623" ref="K374"/>
+    <hyperlink r:id="rId624" ref="AJ374"/>
+    <hyperlink r:id="rId625" ref="K375"/>
+    <hyperlink r:id="rId626" ref="AJ375"/>
+    <hyperlink r:id="rId627" ref="K376"/>
+    <hyperlink r:id="rId628" ref="AJ376"/>
+    <hyperlink r:id="rId629" ref="K377"/>
+    <hyperlink r:id="rId630" ref="AJ377"/>
+    <hyperlink r:id="rId631" ref="K378"/>
+    <hyperlink r:id="rId632" ref="AJ378"/>
+    <hyperlink r:id="rId633" ref="K379"/>
+    <hyperlink r:id="rId634" ref="AJ379"/>
+    <hyperlink r:id="rId635" ref="K380"/>
+    <hyperlink r:id="rId636" ref="AJ380"/>
+    <hyperlink r:id="rId637" ref="K381"/>
+    <hyperlink r:id="rId638" ref="AJ381"/>
+    <hyperlink r:id="rId639" ref="K382"/>
+    <hyperlink r:id="rId640" ref="AJ382"/>
+    <hyperlink r:id="rId641" ref="K383"/>
+    <hyperlink r:id="rId642" ref="AJ383"/>
+    <hyperlink r:id="rId643" ref="K384"/>
+    <hyperlink r:id="rId644" ref="AJ384"/>
+    <hyperlink r:id="rId645" ref="K385"/>
+    <hyperlink r:id="rId646" ref="AJ385"/>
+    <hyperlink r:id="rId647" ref="K386"/>
+    <hyperlink r:id="rId648" ref="Y386"/>
+    <hyperlink r:id="rId649" ref="AA386"/>
+    <hyperlink r:id="rId650" ref="AJ386"/>
+    <hyperlink r:id="rId651" ref="K387"/>
+    <hyperlink r:id="rId652" ref="AJ387"/>
+    <hyperlink r:id="rId653" ref="K388"/>
+    <hyperlink r:id="rId654" ref="AJ388"/>
+    <hyperlink r:id="rId655" ref="K389"/>
+    <hyperlink r:id="rId656" ref="AJ389"/>
+    <hyperlink r:id="rId657" ref="K390"/>
+    <hyperlink r:id="rId658" ref="AJ390"/>
+    <hyperlink r:id="rId659" ref="K391"/>
+    <hyperlink r:id="rId660" ref="AJ391"/>
+    <hyperlink r:id="rId661" ref="K392"/>
+    <hyperlink r:id="rId662" ref="AJ392"/>
+    <hyperlink r:id="rId663" ref="K393"/>
+    <hyperlink r:id="rId664" ref="AJ393"/>
+    <hyperlink r:id="rId665" ref="K394"/>
+    <hyperlink r:id="rId666" ref="AJ394"/>
+    <hyperlink r:id="rId667" ref="K395"/>
+    <hyperlink r:id="rId668" ref="AJ395"/>
+    <hyperlink r:id="rId669" ref="K396"/>
+    <hyperlink r:id="rId670" ref="AJ396"/>
+    <hyperlink r:id="rId671" ref="K397"/>
+    <hyperlink r:id="rId672" ref="AJ397"/>
+    <hyperlink r:id="rId673" ref="K398"/>
+    <hyperlink r:id="rId674" ref="AJ398"/>
+    <hyperlink r:id="rId675" ref="K399"/>
+    <hyperlink r:id="rId676" ref="AJ399"/>
+    <hyperlink r:id="rId677" ref="K400"/>
+    <hyperlink r:id="rId678" ref="AJ400"/>
+    <hyperlink r:id="rId679" ref="K401"/>
+    <hyperlink r:id="rId680" ref="AJ401"/>
+    <hyperlink r:id="rId681" ref="K402"/>
+    <hyperlink r:id="rId682" ref="AJ402"/>
+    <hyperlink r:id="rId683" ref="K403"/>
+    <hyperlink r:id="rId684" ref="AJ403"/>
+    <hyperlink r:id="rId685" ref="K404"/>
+    <hyperlink r:id="rId686" ref="AJ404"/>
+    <hyperlink r:id="rId687" ref="K405"/>
+    <hyperlink r:id="rId688" ref="AJ405"/>
+    <hyperlink r:id="rId689" ref="AJ410"/>
+    <hyperlink r:id="rId690" ref="K411"/>
+    <hyperlink r:id="rId691" ref="AJ411"/>
+    <hyperlink r:id="rId692" ref="K412"/>
+    <hyperlink r:id="rId693" ref="K413"/>
+    <hyperlink r:id="rId694" ref="AJ413"/>
+    <hyperlink r:id="rId695" ref="AJ414"/>
+    <hyperlink r:id="rId696" ref="AK415"/>
+    <hyperlink r:id="rId697" ref="AL415"/>
+    <hyperlink r:id="rId698" ref="K417"/>
+    <hyperlink r:id="rId699" ref="AJ417"/>
+    <hyperlink r:id="rId700" ref="K418"/>
+    <hyperlink r:id="rId701" ref="AJ418"/>
+    <hyperlink r:id="rId702" ref="K419"/>
+    <hyperlink r:id="rId703" ref="AJ419"/>
+    <hyperlink r:id="rId704" ref="K420"/>
+    <hyperlink r:id="rId705" ref="AJ420"/>
+    <hyperlink r:id="rId706" ref="K423"/>
+    <hyperlink r:id="rId707" ref="AJ423"/>
+    <hyperlink r:id="rId708" ref="AK423"/>
+    <hyperlink r:id="rId709" ref="K424"/>
+    <hyperlink r:id="rId710" ref="AJ424"/>
+    <hyperlink r:id="rId711" ref="AL425"/>
+    <hyperlink r:id="rId712" ref="K426"/>
+    <hyperlink r:id="rId713" ref="AJ426"/>
+    <hyperlink r:id="rId714" ref="K427"/>
+    <hyperlink r:id="rId715" ref="AG427"/>
+    <hyperlink r:id="rId716" ref="AJ427"/>
+    <hyperlink r:id="rId717" ref="K428"/>
+    <hyperlink r:id="rId718" ref="AJ428"/>
+    <hyperlink r:id="rId719" ref="K429"/>
+    <hyperlink r:id="rId720" ref="AJ429"/>
+    <hyperlink r:id="rId721" ref="K430"/>
+    <hyperlink r:id="rId722" ref="AJ430"/>
+    <hyperlink r:id="rId723" ref="K431"/>
+    <hyperlink r:id="rId724" ref="AJ431"/>
+    <hyperlink r:id="rId725" ref="K432"/>
+    <hyperlink r:id="rId726" ref="AJ432"/>
+    <hyperlink r:id="rId727" ref="K433"/>
+    <hyperlink r:id="rId728" ref="AJ433"/>
+    <hyperlink r:id="rId729" ref="K434"/>
+    <hyperlink r:id="rId730" ref="AJ434"/>
+    <hyperlink r:id="rId731" ref="K435"/>
+    <hyperlink r:id="rId732" ref="K436"/>
+    <hyperlink r:id="rId733" ref="AJ436"/>
+    <hyperlink r:id="rId734" ref="K437"/>
+    <hyperlink r:id="rId735" ref="AJ437"/>
+    <hyperlink r:id="rId736" ref="K438"/>
+    <hyperlink r:id="rId737" ref="AJ438"/>
+    <hyperlink r:id="rId738" ref="AJ439"/>
+    <hyperlink r:id="rId739" ref="K440"/>
+    <hyperlink r:id="rId740" ref="AJ440"/>
+    <hyperlink r:id="rId741" ref="K441"/>
+    <hyperlink r:id="rId742" ref="AJ441"/>
+    <hyperlink r:id="rId743" ref="K442"/>
+    <hyperlink r:id="rId744" ref="AJ442"/>
+    <hyperlink r:id="rId745" ref="K443"/>
+    <hyperlink r:id="rId746" ref="AJ443"/>
+    <hyperlink r:id="rId747" ref="K445"/>
+    <hyperlink r:id="rId748" ref="AJ445"/>
+    <hyperlink r:id="rId749" ref="K446"/>
+    <hyperlink r:id="rId750" ref="K447"/>
+    <hyperlink r:id="rId751" ref="AA447"/>
+    <hyperlink r:id="rId752" ref="K448"/>
+    <hyperlink r:id="rId753" ref="AJ448"/>
+    <hyperlink r:id="rId754" ref="K449"/>
+    <hyperlink r:id="rId755" ref="AJ449"/>
+    <hyperlink r:id="rId756" ref="K450"/>
+    <hyperlink r:id="rId757" ref="AG450"/>
+    <hyperlink r:id="rId758" ref="AJ450"/>
+    <hyperlink r:id="rId759" ref="K451"/>
+    <hyperlink r:id="rId760" ref="AG451"/>
+    <hyperlink r:id="rId761" ref="AJ451"/>
+    <hyperlink r:id="rId762" ref="K452"/>
+    <hyperlink r:id="rId763" ref="AJ452"/>
+    <hyperlink r:id="rId764" ref="K453"/>
+    <hyperlink r:id="rId765" ref="AJ453"/>
+    <hyperlink r:id="rId766" ref="K454"/>
+    <hyperlink r:id="rId767" ref="AJ454"/>
+    <hyperlink r:id="rId768" ref="K455"/>
+    <hyperlink r:id="rId769" ref="AJ455"/>
+    <hyperlink r:id="rId770" ref="K456"/>
+    <hyperlink r:id="rId771" ref="Y456"/>
+    <hyperlink r:id="rId772" ref="AJ456"/>
+    <hyperlink r:id="rId773" ref="K457"/>
+    <hyperlink r:id="rId774" ref="AJ457"/>
+    <hyperlink r:id="rId775" ref="K458"/>
+    <hyperlink r:id="rId776" ref="AJ458"/>
+    <hyperlink r:id="rId777" ref="K459"/>
+    <hyperlink r:id="rId778" ref="AJ459"/>
+    <hyperlink r:id="rId779" ref="K461"/>
+    <hyperlink r:id="rId780" ref="AG461"/>
+    <hyperlink r:id="rId781" ref="AJ461"/>
+    <hyperlink r:id="rId782" ref="K462"/>
+    <hyperlink r:id="rId783" ref="AJ462"/>
+    <hyperlink r:id="rId784" ref="AT462"/>
+    <hyperlink r:id="rId785" ref="K463"/>
+    <hyperlink r:id="rId786" ref="AJ463"/>
+    <hyperlink r:id="rId787" ref="K464"/>
+    <hyperlink r:id="rId788" ref="AJ464"/>
+    <hyperlink r:id="rId789" ref="K466"/>
+    <hyperlink r:id="rId790" ref="K468"/>
+    <hyperlink r:id="rId791" ref="AJ468"/>
+    <hyperlink r:id="rId792" ref="K470"/>
+    <hyperlink r:id="rId793" ref="AJ470"/>
+    <hyperlink r:id="rId794" ref="K471"/>
+    <hyperlink r:id="rId795" ref="Y471"/>
+    <hyperlink r:id="rId796" ref="AJ471"/>
+    <hyperlink r:id="rId797" ref="K472"/>
+    <hyperlink r:id="rId798" ref="AJ472"/>
+    <hyperlink r:id="rId799" ref="K473"/>
+    <hyperlink r:id="rId800" ref="AJ473"/>
+    <hyperlink r:id="rId801" ref="K474"/>
+    <hyperlink r:id="rId802" ref="AJ474"/>
+    <hyperlink r:id="rId803" ref="K475"/>
+    <hyperlink r:id="rId804" ref="AJ475"/>
+    <hyperlink r:id="rId805" ref="AK476"/>
+    <hyperlink r:id="rId806" ref="K477"/>
+    <hyperlink r:id="rId807" ref="K478"/>
+    <hyperlink r:id="rId808" ref="AJ478"/>
+    <hyperlink r:id="rId809" ref="K479"/>
+    <hyperlink r:id="rId810" ref="AJ479"/>
+    <hyperlink r:id="rId811" ref="K480"/>
+    <hyperlink r:id="rId812" ref="AJ480"/>
+    <hyperlink r:id="rId813" ref="K481"/>
+    <hyperlink r:id="rId814" ref="AJ481"/>
+    <hyperlink r:id="rId815" ref="K482"/>
+    <hyperlink r:id="rId816" ref="AK482"/>
+    <hyperlink r:id="rId817" ref="K483"/>
+    <hyperlink r:id="rId818" ref="AJ483"/>
+    <hyperlink r:id="rId819" ref="K484"/>
+    <hyperlink r:id="rId820" ref="AJ484"/>
+    <hyperlink r:id="rId821" ref="K485"/>
+    <hyperlink r:id="rId822" ref="AJ485"/>
+    <hyperlink r:id="rId823" ref="K486"/>
+    <hyperlink r:id="rId824" ref="AJ486"/>
+    <hyperlink r:id="rId825" ref="K487"/>
+    <hyperlink r:id="rId826" ref="K488"/>
+    <hyperlink r:id="rId827" ref="AJ488"/>
+    <hyperlink r:id="rId828" ref="K489"/>
+    <hyperlink r:id="rId829" ref="AJ489"/>
+    <hyperlink r:id="rId830" ref="K490"/>
+    <hyperlink r:id="rId831" ref="AJ490"/>
+    <hyperlink r:id="rId832" ref="AT492"/>
+    <hyperlink r:id="rId833" ref="K493"/>
+    <hyperlink r:id="rId834" ref="AJ493"/>
+    <hyperlink r:id="rId835" ref="K494"/>
+    <hyperlink r:id="rId836" ref="AJ494"/>
+    <hyperlink r:id="rId837" ref="K495"/>
+    <hyperlink r:id="rId838" ref="Y495"/>
+    <hyperlink r:id="rId839" ref="AJ495"/>
+    <hyperlink r:id="rId840" ref="K496"/>
+    <hyperlink r:id="rId841" ref="AJ496"/>
+    <hyperlink r:id="rId842" ref="K497"/>
+    <hyperlink r:id="rId843" ref="AJ497"/>
+    <hyperlink r:id="rId844" ref="K498"/>
+    <hyperlink r:id="rId845" ref="AJ498"/>
+    <hyperlink r:id="rId846" ref="K499"/>
+    <hyperlink r:id="rId847" ref="AJ499"/>
+    <hyperlink r:id="rId848" ref="K500"/>
+    <hyperlink r:id="rId849" ref="AJ500"/>
+    <hyperlink r:id="rId850" ref="K501"/>
+    <hyperlink r:id="rId851" ref="AJ501"/>
+    <hyperlink r:id="rId852" ref="AT501"/>
+    <hyperlink r:id="rId853" ref="K502"/>
+    <hyperlink r:id="rId854" ref="AJ502"/>
+    <hyperlink r:id="rId855" ref="K503"/>
+    <hyperlink r:id="rId856" ref="AJ503"/>
+    <hyperlink r:id="rId857" ref="K504"/>
+    <hyperlink r:id="rId858" ref="AJ504"/>
+    <hyperlink r:id="rId859" ref="K505"/>
+    <hyperlink r:id="rId860" ref="AJ505"/>
+    <hyperlink r:id="rId861" ref="K506"/>
+    <hyperlink r:id="rId862" ref="Y506"/>
+    <hyperlink r:id="rId863" ref="AJ506"/>
+    <hyperlink r:id="rId864" ref="K507"/>
+    <hyperlink r:id="rId865" ref="Y507"/>
+    <hyperlink r:id="rId866" ref="AJ507"/>
+    <hyperlink r:id="rId867" ref="K508"/>
+    <hyperlink r:id="rId868" ref="AJ508"/>
+    <hyperlink r:id="rId869" ref="K509"/>
+    <hyperlink r:id="rId870" ref="AJ509"/>
+    <hyperlink r:id="rId871" ref="K510"/>
+    <hyperlink r:id="rId872" ref="AJ510"/>
+    <hyperlink r:id="rId873" ref="K511"/>
+    <hyperlink r:id="rId874" ref="AJ511"/>
+    <hyperlink r:id="rId875" ref="AT511"/>
+    <hyperlink r:id="rId876" ref="K512"/>
+    <hyperlink r:id="rId877" ref="AT512"/>
+    <hyperlink r:id="rId878" ref="K513"/>
+    <hyperlink r:id="rId879" ref="AJ513"/>
+    <hyperlink r:id="rId880" ref="AT513"/>
+    <hyperlink r:id="rId881" ref="AJ514"/>
+    <hyperlink r:id="rId882" ref="K515"/>
+    <hyperlink r:id="rId883" ref="AJ515"/>
+    <hyperlink r:id="rId884" ref="K517"/>
+    <hyperlink r:id="rId885" ref="AJ517"/>
+    <hyperlink r:id="rId886" ref="K518"/>
+    <hyperlink r:id="rId887" ref="AJ518"/>
+    <hyperlink r:id="rId888" ref="K520"/>
+    <hyperlink r:id="rId889" ref="AJ520"/>
+    <hyperlink r:id="rId890" ref="K521"/>
+    <hyperlink r:id="rId891" ref="AJ521"/>
+    <hyperlink r:id="rId892" ref="AT524"/>
+    <hyperlink r:id="rId893" ref="K525"/>
+    <hyperlink r:id="rId894" ref="AJ525"/>
+    <hyperlink r:id="rId895" ref="K526"/>
+    <hyperlink r:id="rId896" ref="AJ526"/>
+    <hyperlink r:id="rId897" ref="K527"/>
+    <hyperlink r:id="rId898" ref="AJ527"/>
+    <hyperlink r:id="rId899" ref="K528"/>
+    <hyperlink r:id="rId900" ref="AJ528"/>
+    <hyperlink r:id="rId901" ref="K529"/>
+    <hyperlink r:id="rId902" ref="AJ529"/>
+    <hyperlink r:id="rId903" ref="K530"/>
+    <hyperlink r:id="rId904" ref="AJ530"/>
+    <hyperlink r:id="rId905" ref="K531"/>
+    <hyperlink r:id="rId906" ref="AJ531"/>
+    <hyperlink r:id="rId907" ref="K532"/>
+    <hyperlink r:id="rId908" ref="AK532"/>
+    <hyperlink r:id="rId909" ref="K533"/>
+    <hyperlink r:id="rId910" ref="AJ533"/>
+    <hyperlink r:id="rId911" ref="K534"/>
+    <hyperlink r:id="rId912" ref="AJ534"/>
+    <hyperlink r:id="rId913" ref="K535"/>
+    <hyperlink r:id="rId914" ref="AJ535"/>
+    <hyperlink r:id="rId915" ref="K536"/>
+    <hyperlink r:id="rId916" ref="AJ536"/>
+    <hyperlink r:id="rId917" ref="K537"/>
+    <hyperlink r:id="rId918" ref="AJ537"/>
+    <hyperlink r:id="rId919" ref="K538"/>
+    <hyperlink r:id="rId920" ref="AJ538"/>
+    <hyperlink r:id="rId921" ref="AT538"/>
+    <hyperlink r:id="rId922" ref="K539"/>
+    <hyperlink r:id="rId923" ref="Y539"/>
+    <hyperlink r:id="rId924" ref="AJ539"/>
+    <hyperlink r:id="rId925" ref="K540"/>
+    <hyperlink r:id="rId926" ref="AJ540"/>
   </hyperlinks>
   <printOptions/>
   <pageMargins bottom="0.984027777777778" footer="0.0" header="0.0" left="0.747916666666667" right="0.747916666666667" top="0.984027777777778"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <drawing r:id="rId929"/>
+  <drawing r:id="rId927"/>
 </worksheet>
 </file>
--- a/data/PPDB database.xlsx
+++ b/data/PPDB database.xlsx
@@ -4000,7 +4000,7 @@
     <t>Священная митрополия Абхазии</t>
   </si>
   <si>
-    <t>https://abkhazia.church/wp-content/themes/anyha_new/images/logo.png</t>
+    <t>/media/logos/geHMA.png</t>
   </si>
   <si>
     <t>#0f5b91</t>
@@ -28372,7 +28372,7 @@
       <c r="H126" s="2"/>
       <c r="I126" s="2"/>
       <c r="J126" s="2"/>
-      <c r="K126" s="8" t="s">
+      <c r="K126" s="5" t="s">
         <v>1100</v>
       </c>
       <c r="L126" s="5" t="s">
@@ -80128,748 +80128,747 @@
     <hyperlink r:id="rId202" ref="AJ122"/>
     <hyperlink r:id="rId203" ref="K125"/>
     <hyperlink r:id="rId204" ref="AJ125"/>
-    <hyperlink r:id="rId205" ref="K126"/>
-    <hyperlink r:id="rId206" ref="Y126"/>
-    <hyperlink r:id="rId207" ref="AJ126"/>
-    <hyperlink r:id="rId208" ref="AJ127"/>
-    <hyperlink r:id="rId209" ref="K128"/>
-    <hyperlink r:id="rId210" ref="AJ128"/>
-    <hyperlink r:id="rId211" ref="K130"/>
-    <hyperlink r:id="rId212" ref="AJ130"/>
-    <hyperlink r:id="rId213" ref="K131"/>
-    <hyperlink r:id="rId214" ref="AJ131"/>
-    <hyperlink r:id="rId215" ref="K132"/>
-    <hyperlink r:id="rId216" ref="K133"/>
-    <hyperlink r:id="rId217" ref="AJ133"/>
-    <hyperlink r:id="rId218" ref="K134"/>
-    <hyperlink r:id="rId219" ref="AJ134"/>
-    <hyperlink r:id="rId220" ref="K135"/>
-    <hyperlink r:id="rId221" ref="AJ135"/>
-    <hyperlink r:id="rId222" ref="K136"/>
-    <hyperlink r:id="rId223" ref="AJ136"/>
-    <hyperlink r:id="rId224" ref="K137"/>
-    <hyperlink r:id="rId225" ref="AJ137"/>
-    <hyperlink r:id="rId226" ref="K138"/>
-    <hyperlink r:id="rId227" ref="K139"/>
-    <hyperlink r:id="rId228" ref="AJ139"/>
-    <hyperlink r:id="rId229" ref="K140"/>
-    <hyperlink r:id="rId230" ref="AJ140"/>
-    <hyperlink r:id="rId231" ref="K141"/>
-    <hyperlink r:id="rId232" ref="AK141"/>
-    <hyperlink r:id="rId233" ref="K142"/>
-    <hyperlink r:id="rId234" ref="AK142"/>
-    <hyperlink r:id="rId235" ref="K143"/>
-    <hyperlink r:id="rId236" ref="AK143"/>
-    <hyperlink r:id="rId237" ref="K144"/>
-    <hyperlink r:id="rId238" ref="AK144"/>
-    <hyperlink r:id="rId239" ref="K145"/>
-    <hyperlink r:id="rId240" ref="AK145"/>
-    <hyperlink r:id="rId241" ref="K146"/>
-    <hyperlink r:id="rId242" ref="AJ146"/>
-    <hyperlink r:id="rId243" ref="K147"/>
-    <hyperlink r:id="rId244" ref="AJ147"/>
-    <hyperlink r:id="rId245" ref="K148"/>
-    <hyperlink r:id="rId246" ref="AJ148"/>
-    <hyperlink r:id="rId247" ref="K149"/>
-    <hyperlink r:id="rId248" ref="AJ149"/>
-    <hyperlink r:id="rId249" ref="K150"/>
-    <hyperlink r:id="rId250" ref="AJ150"/>
-    <hyperlink r:id="rId251" ref="K151"/>
-    <hyperlink r:id="rId252" ref="AJ151"/>
-    <hyperlink r:id="rId253" ref="K152"/>
-    <hyperlink r:id="rId254" ref="AJ152"/>
-    <hyperlink r:id="rId255" ref="K153"/>
-    <hyperlink r:id="rId256" ref="AJ153"/>
-    <hyperlink r:id="rId257" ref="K154"/>
-    <hyperlink r:id="rId258" ref="AJ154"/>
-    <hyperlink r:id="rId259" ref="K155"/>
-    <hyperlink r:id="rId260" ref="AJ155"/>
-    <hyperlink r:id="rId261" ref="K156"/>
-    <hyperlink r:id="rId262" ref="AJ156"/>
-    <hyperlink r:id="rId263" ref="K157"/>
-    <hyperlink r:id="rId264" ref="AJ157"/>
-    <hyperlink r:id="rId265" ref="K158"/>
-    <hyperlink r:id="rId266" ref="AJ158"/>
-    <hyperlink r:id="rId267" ref="K162"/>
-    <hyperlink r:id="rId268" ref="AJ162"/>
-    <hyperlink r:id="rId269" ref="K165"/>
-    <hyperlink r:id="rId270" ref="AJ165"/>
-    <hyperlink r:id="rId271" ref="K166"/>
-    <hyperlink r:id="rId272" ref="K167"/>
-    <hyperlink r:id="rId273" ref="K170"/>
-    <hyperlink r:id="rId274" ref="AK170"/>
-    <hyperlink r:id="rId275" ref="K171"/>
-    <hyperlink r:id="rId276" ref="Y171"/>
-    <hyperlink r:id="rId277" ref="K172"/>
-    <hyperlink r:id="rId278" ref="AK172"/>
-    <hyperlink r:id="rId279" ref="K173"/>
-    <hyperlink r:id="rId280" ref="AJ173"/>
-    <hyperlink r:id="rId281" ref="K176"/>
-    <hyperlink r:id="rId282" ref="AJ176"/>
-    <hyperlink r:id="rId283" ref="K177"/>
-    <hyperlink r:id="rId284" ref="AJ177"/>
-    <hyperlink r:id="rId285" ref="K178"/>
-    <hyperlink r:id="rId286" ref="AG178"/>
-    <hyperlink r:id="rId287" ref="AJ178"/>
-    <hyperlink r:id="rId288" ref="K179"/>
-    <hyperlink r:id="rId289" ref="K180"/>
-    <hyperlink r:id="rId290" ref="AJ180"/>
-    <hyperlink r:id="rId291" ref="K184"/>
-    <hyperlink r:id="rId292" ref="AJ184"/>
-    <hyperlink r:id="rId293" ref="K185"/>
-    <hyperlink r:id="rId294" ref="AJ185"/>
-    <hyperlink r:id="rId295" ref="K187"/>
-    <hyperlink r:id="rId296" ref="AJ187"/>
-    <hyperlink r:id="rId297" ref="AJ188"/>
-    <hyperlink r:id="rId298" ref="K189"/>
-    <hyperlink r:id="rId299" ref="K190"/>
-    <hyperlink r:id="rId300" ref="AJ190"/>
-    <hyperlink r:id="rId301" ref="K191"/>
-    <hyperlink r:id="rId302" ref="AJ191"/>
-    <hyperlink r:id="rId303" ref="K192"/>
-    <hyperlink r:id="rId304" ref="AJ192"/>
-    <hyperlink r:id="rId305" ref="K193"/>
-    <hyperlink r:id="rId306" ref="AJ193"/>
-    <hyperlink r:id="rId307" ref="AJ194"/>
-    <hyperlink r:id="rId308" ref="AT194"/>
-    <hyperlink r:id="rId309" ref="AT195"/>
-    <hyperlink r:id="rId310" ref="K196"/>
-    <hyperlink r:id="rId311" ref="AK196"/>
-    <hyperlink r:id="rId312" ref="K197"/>
-    <hyperlink r:id="rId313" ref="AJ197"/>
-    <hyperlink r:id="rId314" ref="K198"/>
-    <hyperlink r:id="rId315" ref="AJ198"/>
-    <hyperlink r:id="rId316" ref="K199"/>
-    <hyperlink r:id="rId317" ref="AJ199"/>
-    <hyperlink r:id="rId318" ref="K200"/>
-    <hyperlink r:id="rId319" ref="AJ200"/>
-    <hyperlink r:id="rId320" ref="K201"/>
-    <hyperlink r:id="rId321" ref="AJ201"/>
-    <hyperlink r:id="rId322" ref="K202"/>
-    <hyperlink r:id="rId323" ref="Y202"/>
-    <hyperlink r:id="rId324" ref="AJ202"/>
-    <hyperlink r:id="rId325" ref="K203"/>
-    <hyperlink r:id="rId326" ref="AJ203"/>
-    <hyperlink r:id="rId327" ref="K204"/>
-    <hyperlink r:id="rId328" ref="Y204"/>
-    <hyperlink r:id="rId329" ref="AJ204"/>
-    <hyperlink r:id="rId330" ref="K205"/>
-    <hyperlink r:id="rId331" ref="AJ205"/>
-    <hyperlink r:id="rId332" ref="K206"/>
-    <hyperlink r:id="rId333" ref="AJ206"/>
-    <hyperlink r:id="rId334" ref="K207"/>
-    <hyperlink r:id="rId335" ref="AJ207"/>
-    <hyperlink r:id="rId336" ref="K208"/>
-    <hyperlink r:id="rId337" ref="AJ208"/>
-    <hyperlink r:id="rId338" ref="K209"/>
-    <hyperlink r:id="rId339" ref="AJ209"/>
-    <hyperlink r:id="rId340" ref="K210"/>
-    <hyperlink r:id="rId341" ref="AJ210"/>
-    <hyperlink r:id="rId342" ref="K211"/>
-    <hyperlink r:id="rId343" ref="AJ211"/>
-    <hyperlink r:id="rId344" ref="AJ212"/>
-    <hyperlink r:id="rId345" ref="K213"/>
-    <hyperlink r:id="rId346" ref="AT214"/>
-    <hyperlink r:id="rId347" ref="K215"/>
-    <hyperlink r:id="rId348" ref="AJ215"/>
-    <hyperlink r:id="rId349" ref="K216"/>
-    <hyperlink r:id="rId350" ref="AJ216"/>
-    <hyperlink r:id="rId351" location="v=onepage&amp;q&amp;f=false" ref="AT216"/>
-    <hyperlink r:id="rId352" ref="K217"/>
-    <hyperlink r:id="rId353" ref="AJ217"/>
-    <hyperlink r:id="rId354" ref="AL217"/>
-    <hyperlink r:id="rId355" ref="AO217"/>
-    <hyperlink r:id="rId356" ref="AJ218"/>
-    <hyperlink r:id="rId357" ref="AM218"/>
-    <hyperlink r:id="rId358" location="v=onepage&amp;q&amp;f=false" ref="AT218"/>
-    <hyperlink r:id="rId359" ref="K219"/>
-    <hyperlink r:id="rId360" ref="AK219"/>
-    <hyperlink r:id="rId361" ref="K220"/>
-    <hyperlink r:id="rId362" ref="AJ220"/>
-    <hyperlink r:id="rId363" ref="K221"/>
-    <hyperlink r:id="rId364" ref="AJ221"/>
-    <hyperlink r:id="rId365" ref="K222"/>
-    <hyperlink r:id="rId366" ref="AJ222"/>
-    <hyperlink r:id="rId367" ref="K223"/>
-    <hyperlink r:id="rId368" ref="AJ223"/>
-    <hyperlink r:id="rId369" ref="K224"/>
-    <hyperlink r:id="rId370" ref="AJ224"/>
-    <hyperlink r:id="rId371" ref="K226"/>
-    <hyperlink r:id="rId372" ref="AJ226"/>
-    <hyperlink r:id="rId373" ref="K227"/>
-    <hyperlink r:id="rId374" ref="AJ227"/>
-    <hyperlink r:id="rId375" ref="K228"/>
-    <hyperlink r:id="rId376" ref="K229"/>
-    <hyperlink r:id="rId377" ref="AJ229"/>
-    <hyperlink r:id="rId378" ref="K231"/>
-    <hyperlink r:id="rId379" ref="AJ231"/>
-    <hyperlink r:id="rId380" ref="K233"/>
-    <hyperlink r:id="rId381" ref="AJ233"/>
-    <hyperlink r:id="rId382" ref="K235"/>
-    <hyperlink r:id="rId383" ref="AJ235"/>
-    <hyperlink r:id="rId384" ref="K236"/>
-    <hyperlink r:id="rId385" ref="AJ236"/>
-    <hyperlink r:id="rId386" ref="AT237"/>
-    <hyperlink r:id="rId387" ref="K238"/>
-    <hyperlink r:id="rId388" ref="AJ238"/>
-    <hyperlink r:id="rId389" ref="K239"/>
-    <hyperlink r:id="rId390" ref="AJ239"/>
-    <hyperlink r:id="rId391" ref="K240"/>
-    <hyperlink r:id="rId392" ref="AL240"/>
-    <hyperlink r:id="rId393" ref="K241"/>
-    <hyperlink r:id="rId394" ref="AJ241"/>
-    <hyperlink r:id="rId395" ref="K242"/>
-    <hyperlink r:id="rId396" ref="AJ242"/>
-    <hyperlink r:id="rId397" ref="K245"/>
-    <hyperlink r:id="rId398" ref="K246"/>
-    <hyperlink r:id="rId399" ref="AJ246"/>
-    <hyperlink r:id="rId400" ref="K247"/>
-    <hyperlink r:id="rId401" ref="AJ247"/>
-    <hyperlink r:id="rId402" ref="K249"/>
-    <hyperlink r:id="rId403" ref="AJ249"/>
-    <hyperlink r:id="rId404" ref="K250"/>
-    <hyperlink r:id="rId405" ref="K252"/>
-    <hyperlink r:id="rId406" ref="AJ252"/>
-    <hyperlink r:id="rId407" ref="K253"/>
-    <hyperlink r:id="rId408" ref="AK253"/>
-    <hyperlink r:id="rId409" ref="AT253"/>
-    <hyperlink r:id="rId410" ref="K254"/>
-    <hyperlink r:id="rId411" ref="AJ254"/>
-    <hyperlink r:id="rId412" ref="K255"/>
-    <hyperlink r:id="rId413" ref="AJ255"/>
-    <hyperlink r:id="rId414" ref="AJ256"/>
-    <hyperlink r:id="rId415" ref="K259"/>
-    <hyperlink r:id="rId416" ref="AJ259"/>
-    <hyperlink r:id="rId417" ref="K260"/>
-    <hyperlink r:id="rId418" ref="AJ260"/>
-    <hyperlink r:id="rId419" ref="K261"/>
-    <hyperlink r:id="rId420" ref="AJ261"/>
-    <hyperlink r:id="rId421" ref="K262"/>
-    <hyperlink r:id="rId422" ref="AJ262"/>
-    <hyperlink r:id="rId423" ref="K263"/>
-    <hyperlink r:id="rId424" ref="AJ263"/>
-    <hyperlink r:id="rId425" ref="K264"/>
-    <hyperlink r:id="rId426" ref="Y264"/>
-    <hyperlink r:id="rId427" ref="AJ264"/>
-    <hyperlink r:id="rId428" ref="K265"/>
-    <hyperlink r:id="rId429" ref="AJ265"/>
-    <hyperlink r:id="rId430" ref="K266"/>
-    <hyperlink r:id="rId431" ref="AJ266"/>
-    <hyperlink r:id="rId432" ref="K267"/>
-    <hyperlink r:id="rId433" ref="AJ267"/>
-    <hyperlink r:id="rId434" ref="K268"/>
-    <hyperlink r:id="rId435" ref="AJ268"/>
-    <hyperlink r:id="rId436" ref="K269"/>
-    <hyperlink r:id="rId437" ref="AJ269"/>
-    <hyperlink r:id="rId438" ref="K271"/>
-    <hyperlink r:id="rId439" ref="AJ271"/>
-    <hyperlink r:id="rId440" location="v=onepage&amp;q=%22Deutschen%20Evangelischen%20Synode%20von%20S%C3%BCdwestafrika%22&amp;f=false" ref="AT271"/>
-    <hyperlink r:id="rId441" ref="K272"/>
-    <hyperlink r:id="rId442" ref="AK272"/>
-    <hyperlink r:id="rId443" ref="K273"/>
-    <hyperlink r:id="rId444" ref="AJ273"/>
-    <hyperlink r:id="rId445" ref="AT274"/>
-    <hyperlink r:id="rId446" ref="K275"/>
-    <hyperlink r:id="rId447" ref="AJ275"/>
-    <hyperlink r:id="rId448" ref="K276"/>
-    <hyperlink r:id="rId449" ref="AJ276"/>
-    <hyperlink r:id="rId450" ref="K277"/>
-    <hyperlink r:id="rId451" ref="AJ277"/>
-    <hyperlink r:id="rId452" ref="K278"/>
-    <hyperlink r:id="rId453" ref="AJ278"/>
-    <hyperlink r:id="rId454" ref="K279"/>
-    <hyperlink r:id="rId455" ref="AJ279"/>
-    <hyperlink r:id="rId456" ref="K280"/>
-    <hyperlink r:id="rId457" ref="AJ280"/>
-    <hyperlink r:id="rId458" ref="AJ281"/>
-    <hyperlink r:id="rId459" ref="K282"/>
-    <hyperlink r:id="rId460" ref="AJ282"/>
-    <hyperlink r:id="rId461" ref="K283"/>
-    <hyperlink r:id="rId462" ref="AJ283"/>
-    <hyperlink r:id="rId463" ref="K284"/>
-    <hyperlink r:id="rId464" ref="AJ284"/>
-    <hyperlink r:id="rId465" ref="K285"/>
-    <hyperlink r:id="rId466" ref="Y285"/>
-    <hyperlink r:id="rId467" ref="AA285"/>
-    <hyperlink r:id="rId468" ref="K286"/>
-    <hyperlink r:id="rId469" ref="AJ286"/>
-    <hyperlink r:id="rId470" ref="K287"/>
-    <hyperlink r:id="rId471" ref="AJ287"/>
-    <hyperlink r:id="rId472" ref="AT287"/>
-    <hyperlink r:id="rId473" ref="K288"/>
-    <hyperlink r:id="rId474" ref="AJ288"/>
-    <hyperlink r:id="rId475" ref="K289"/>
-    <hyperlink r:id="rId476" ref="AJ289"/>
-    <hyperlink r:id="rId477" ref="K290"/>
-    <hyperlink r:id="rId478" ref="AJ290"/>
-    <hyperlink r:id="rId479" ref="K291"/>
-    <hyperlink r:id="rId480" ref="AJ291"/>
-    <hyperlink r:id="rId481" ref="K292"/>
-    <hyperlink r:id="rId482" ref="AJ292"/>
-    <hyperlink r:id="rId483" ref="K293"/>
-    <hyperlink r:id="rId484" ref="AA293"/>
-    <hyperlink r:id="rId485" ref="AC293"/>
-    <hyperlink r:id="rId486" ref="AJ293"/>
-    <hyperlink r:id="rId487" ref="AK293"/>
-    <hyperlink r:id="rId488" ref="K296"/>
-    <hyperlink r:id="rId489" ref="AJ296"/>
-    <hyperlink r:id="rId490" ref="K297"/>
-    <hyperlink r:id="rId491" ref="AJ297"/>
-    <hyperlink r:id="rId492" ref="K298"/>
-    <hyperlink r:id="rId493" ref="K299"/>
-    <hyperlink r:id="rId494" ref="AJ299"/>
-    <hyperlink r:id="rId495" ref="K300"/>
-    <hyperlink r:id="rId496" ref="AJ300"/>
-    <hyperlink r:id="rId497" ref="K301"/>
-    <hyperlink r:id="rId498" ref="K302"/>
-    <hyperlink r:id="rId499" ref="Y302"/>
-    <hyperlink r:id="rId500" ref="AK302"/>
-    <hyperlink r:id="rId501" ref="K303"/>
-    <hyperlink r:id="rId502" ref="Y303"/>
-    <hyperlink r:id="rId503" ref="K304"/>
-    <hyperlink r:id="rId504" ref="AJ304"/>
-    <hyperlink r:id="rId505" ref="K305"/>
-    <hyperlink r:id="rId506" ref="AK305"/>
-    <hyperlink r:id="rId507" ref="K306"/>
-    <hyperlink r:id="rId508" ref="AJ306"/>
-    <hyperlink r:id="rId509" ref="K307"/>
-    <hyperlink r:id="rId510" ref="AJ307"/>
-    <hyperlink r:id="rId511" ref="K308"/>
-    <hyperlink r:id="rId512" ref="AJ308"/>
-    <hyperlink r:id="rId513" ref="K309"/>
-    <hyperlink r:id="rId514" ref="K310"/>
-    <hyperlink r:id="rId515" ref="AJ310"/>
-    <hyperlink r:id="rId516" ref="K311"/>
-    <hyperlink r:id="rId517" ref="AL311"/>
-    <hyperlink r:id="rId518" ref="K313"/>
-    <hyperlink r:id="rId519" ref="AJ313"/>
-    <hyperlink r:id="rId520" ref="K314"/>
-    <hyperlink r:id="rId521" ref="Y314"/>
-    <hyperlink r:id="rId522" ref="AJ314"/>
-    <hyperlink r:id="rId523" ref="K315"/>
-    <hyperlink r:id="rId524" ref="AJ315"/>
-    <hyperlink r:id="rId525" ref="K316"/>
-    <hyperlink r:id="rId526" ref="AJ316"/>
-    <hyperlink r:id="rId527" ref="K317"/>
-    <hyperlink r:id="rId528" ref="AJ317"/>
-    <hyperlink r:id="rId529" ref="AL318"/>
-    <hyperlink r:id="rId530" ref="K319"/>
-    <hyperlink r:id="rId531" ref="AL319"/>
-    <hyperlink r:id="rId532" ref="K320"/>
-    <hyperlink r:id="rId533" ref="AJ320"/>
-    <hyperlink r:id="rId534" ref="K321"/>
-    <hyperlink r:id="rId535" ref="AJ321"/>
-    <hyperlink r:id="rId536" ref="K322"/>
-    <hyperlink r:id="rId537" ref="AJ322"/>
-    <hyperlink r:id="rId538" ref="K323"/>
-    <hyperlink r:id="rId539" ref="AL323"/>
-    <hyperlink r:id="rId540" ref="K324"/>
-    <hyperlink r:id="rId541" ref="AJ324"/>
-    <hyperlink r:id="rId542" ref="K325"/>
-    <hyperlink r:id="rId543" ref="AJ325"/>
-    <hyperlink r:id="rId544" ref="K326"/>
-    <hyperlink r:id="rId545" ref="AJ326"/>
-    <hyperlink r:id="rId546" ref="K327"/>
-    <hyperlink r:id="rId547" ref="AJ327"/>
-    <hyperlink r:id="rId548" ref="K330"/>
-    <hyperlink r:id="rId549" ref="AJ330"/>
-    <hyperlink r:id="rId550" ref="K331"/>
-    <hyperlink r:id="rId551" ref="AJ331"/>
-    <hyperlink r:id="rId552" ref="K332"/>
-    <hyperlink r:id="rId553" ref="AJ332"/>
-    <hyperlink r:id="rId554" ref="K333"/>
-    <hyperlink r:id="rId555" ref="AJ333"/>
-    <hyperlink r:id="rId556" ref="K334"/>
-    <hyperlink r:id="rId557" ref="AJ334"/>
-    <hyperlink r:id="rId558" ref="K336"/>
-    <hyperlink r:id="rId559" ref="AJ336"/>
-    <hyperlink r:id="rId560" ref="K337"/>
-    <hyperlink r:id="rId561" ref="AJ337"/>
-    <hyperlink r:id="rId562" ref="K338"/>
-    <hyperlink r:id="rId563" ref="AJ338"/>
-    <hyperlink r:id="rId564" ref="K339"/>
-    <hyperlink r:id="rId565" ref="Y339"/>
-    <hyperlink r:id="rId566" ref="AJ339"/>
-    <hyperlink r:id="rId567" ref="K340"/>
-    <hyperlink r:id="rId568" ref="AJ340"/>
-    <hyperlink r:id="rId569" ref="K341"/>
-    <hyperlink r:id="rId570" ref="AJ341"/>
-    <hyperlink r:id="rId571" ref="K342"/>
-    <hyperlink r:id="rId572" ref="AJ342"/>
-    <hyperlink r:id="rId573" ref="K343"/>
-    <hyperlink r:id="rId574" ref="AJ343"/>
-    <hyperlink r:id="rId575" ref="AJ345"/>
-    <hyperlink r:id="rId576" ref="K347"/>
-    <hyperlink r:id="rId577" ref="K348"/>
-    <hyperlink r:id="rId578" ref="K352"/>
-    <hyperlink r:id="rId579" ref="K353"/>
-    <hyperlink r:id="rId580" ref="AJ353"/>
-    <hyperlink r:id="rId581" ref="K354"/>
-    <hyperlink r:id="rId582" ref="AJ354"/>
-    <hyperlink r:id="rId583" ref="K355"/>
-    <hyperlink r:id="rId584" ref="AJ355"/>
-    <hyperlink r:id="rId585" ref="AJ356"/>
-    <hyperlink r:id="rId586" ref="K357"/>
-    <hyperlink r:id="rId587" ref="AJ357"/>
-    <hyperlink r:id="rId588" ref="K358"/>
-    <hyperlink r:id="rId589" ref="AJ358"/>
-    <hyperlink r:id="rId590" ref="K359"/>
-    <hyperlink r:id="rId591" ref="AK359"/>
-    <hyperlink r:id="rId592" ref="K360"/>
-    <hyperlink r:id="rId593" ref="AJ360"/>
-    <hyperlink r:id="rId594" ref="K361"/>
-    <hyperlink r:id="rId595" ref="AJ361"/>
-    <hyperlink r:id="rId596" ref="K362"/>
-    <hyperlink r:id="rId597" ref="Y362"/>
-    <hyperlink r:id="rId598" ref="AJ362"/>
-    <hyperlink r:id="rId599" ref="K363"/>
-    <hyperlink r:id="rId600" ref="AJ363"/>
-    <hyperlink r:id="rId601" ref="K364"/>
-    <hyperlink r:id="rId602" ref="AJ364"/>
-    <hyperlink r:id="rId603" ref="K365"/>
-    <hyperlink r:id="rId604" ref="AJ365"/>
-    <hyperlink r:id="rId605" ref="K366"/>
-    <hyperlink r:id="rId606" ref="Y366"/>
-    <hyperlink r:id="rId607" ref="AJ366"/>
-    <hyperlink r:id="rId608" ref="K369"/>
-    <hyperlink r:id="rId609" ref="AJ369"/>
-    <hyperlink r:id="rId610" location="v=onepage&amp;q&amp;f=false" ref="AT369"/>
-    <hyperlink r:id="rId611" ref="K370"/>
-    <hyperlink r:id="rId612" ref="AK370"/>
-    <hyperlink r:id="rId613" location="v=onepage&amp;q&amp;f=false" ref="AT370"/>
-    <hyperlink r:id="rId614" ref="K371"/>
-    <hyperlink r:id="rId615" ref="Y371"/>
-    <hyperlink r:id="rId616" ref="AJ371"/>
-    <hyperlink r:id="rId617" ref="K372"/>
-    <hyperlink r:id="rId618" ref="AJ372"/>
-    <hyperlink r:id="rId619" ref="K373"/>
-    <hyperlink r:id="rId620" ref="AJ373"/>
-    <hyperlink r:id="rId621" ref="K374"/>
-    <hyperlink r:id="rId622" ref="AJ374"/>
-    <hyperlink r:id="rId623" ref="AT374"/>
-    <hyperlink r:id="rId624" ref="K375"/>
-    <hyperlink r:id="rId625" ref="AJ375"/>
-    <hyperlink r:id="rId626" ref="K376"/>
-    <hyperlink r:id="rId627" ref="Y376"/>
-    <hyperlink r:id="rId628" ref="AJ376"/>
-    <hyperlink r:id="rId629" ref="K377"/>
-    <hyperlink r:id="rId630" ref="AJ377"/>
-    <hyperlink r:id="rId631" ref="K378"/>
-    <hyperlink r:id="rId632" ref="AJ378"/>
-    <hyperlink r:id="rId633" ref="K379"/>
-    <hyperlink r:id="rId634" ref="AJ379"/>
-    <hyperlink r:id="rId635" ref="K380"/>
-    <hyperlink r:id="rId636" ref="AJ380"/>
-    <hyperlink r:id="rId637" ref="K381"/>
-    <hyperlink r:id="rId638" ref="AJ381"/>
-    <hyperlink r:id="rId639" ref="K382"/>
-    <hyperlink r:id="rId640" ref="AJ382"/>
-    <hyperlink r:id="rId641" ref="K383"/>
-    <hyperlink r:id="rId642" ref="AJ383"/>
-    <hyperlink r:id="rId643" ref="K384"/>
-    <hyperlink r:id="rId644" ref="AJ384"/>
-    <hyperlink r:id="rId645" ref="K385"/>
-    <hyperlink r:id="rId646" ref="AJ385"/>
-    <hyperlink r:id="rId647" ref="K386"/>
-    <hyperlink r:id="rId648" ref="AJ386"/>
-    <hyperlink r:id="rId649" ref="K387"/>
-    <hyperlink r:id="rId650" ref="AJ387"/>
-    <hyperlink r:id="rId651" ref="K388"/>
-    <hyperlink r:id="rId652" ref="AJ388"/>
-    <hyperlink r:id="rId653" ref="K389"/>
-    <hyperlink r:id="rId654" ref="AJ389"/>
-    <hyperlink r:id="rId655" ref="K390"/>
-    <hyperlink r:id="rId656" ref="AJ390"/>
-    <hyperlink r:id="rId657" ref="K391"/>
-    <hyperlink r:id="rId658" ref="AJ391"/>
-    <hyperlink r:id="rId659" ref="K392"/>
-    <hyperlink r:id="rId660" ref="AJ392"/>
-    <hyperlink r:id="rId661" ref="K393"/>
-    <hyperlink r:id="rId662" ref="Y393"/>
-    <hyperlink r:id="rId663" ref="AA393"/>
-    <hyperlink r:id="rId664" ref="AJ393"/>
-    <hyperlink r:id="rId665" ref="K394"/>
-    <hyperlink r:id="rId666" ref="AJ394"/>
-    <hyperlink r:id="rId667" ref="K395"/>
-    <hyperlink r:id="rId668" ref="AJ395"/>
-    <hyperlink r:id="rId669" ref="K396"/>
-    <hyperlink r:id="rId670" ref="AJ396"/>
-    <hyperlink r:id="rId671" ref="K397"/>
-    <hyperlink r:id="rId672" ref="AJ397"/>
-    <hyperlink r:id="rId673" ref="K398"/>
-    <hyperlink r:id="rId674" ref="AJ398"/>
-    <hyperlink r:id="rId675" ref="K399"/>
-    <hyperlink r:id="rId676" ref="AJ399"/>
-    <hyperlink r:id="rId677" ref="K400"/>
-    <hyperlink r:id="rId678" ref="AJ400"/>
-    <hyperlink r:id="rId679" ref="K401"/>
-    <hyperlink r:id="rId680" ref="AJ401"/>
-    <hyperlink r:id="rId681" ref="K402"/>
-    <hyperlink r:id="rId682" ref="AJ402"/>
-    <hyperlink r:id="rId683" ref="K403"/>
-    <hyperlink r:id="rId684" ref="AJ403"/>
-    <hyperlink r:id="rId685" ref="K404"/>
-    <hyperlink r:id="rId686" ref="AJ404"/>
-    <hyperlink r:id="rId687" ref="K405"/>
-    <hyperlink r:id="rId688" ref="AJ405"/>
-    <hyperlink r:id="rId689" ref="K406"/>
-    <hyperlink r:id="rId690" ref="AJ406"/>
-    <hyperlink r:id="rId691" ref="K407"/>
-    <hyperlink r:id="rId692" ref="AJ407"/>
-    <hyperlink r:id="rId693" ref="K408"/>
-    <hyperlink r:id="rId694" ref="AJ408"/>
-    <hyperlink r:id="rId695" ref="K409"/>
-    <hyperlink r:id="rId696" ref="AJ409"/>
-    <hyperlink r:id="rId697" ref="K410"/>
-    <hyperlink r:id="rId698" ref="AJ410"/>
-    <hyperlink r:id="rId699" ref="K411"/>
-    <hyperlink r:id="rId700" ref="AJ411"/>
-    <hyperlink r:id="rId701" ref="K412"/>
-    <hyperlink r:id="rId702" ref="AJ412"/>
-    <hyperlink r:id="rId703" ref="AJ417"/>
-    <hyperlink r:id="rId704" ref="K418"/>
-    <hyperlink r:id="rId705" ref="AJ418"/>
-    <hyperlink r:id="rId706" ref="K419"/>
-    <hyperlink r:id="rId707" ref="K420"/>
-    <hyperlink r:id="rId708" ref="AJ420"/>
-    <hyperlink r:id="rId709" ref="AJ421"/>
-    <hyperlink r:id="rId710" ref="AK422"/>
-    <hyperlink r:id="rId711" ref="AL422"/>
-    <hyperlink r:id="rId712" ref="K424"/>
-    <hyperlink r:id="rId713" ref="AJ424"/>
-    <hyperlink r:id="rId714" ref="K425"/>
-    <hyperlink r:id="rId715" ref="AJ425"/>
-    <hyperlink r:id="rId716" ref="K426"/>
-    <hyperlink r:id="rId717" ref="AJ426"/>
-    <hyperlink r:id="rId718" ref="K427"/>
-    <hyperlink r:id="rId719" ref="AJ427"/>
-    <hyperlink r:id="rId720" ref="K430"/>
-    <hyperlink r:id="rId721" ref="AJ430"/>
-    <hyperlink r:id="rId722" ref="AK430"/>
-    <hyperlink r:id="rId723" ref="K431"/>
-    <hyperlink r:id="rId724" ref="AJ431"/>
-    <hyperlink r:id="rId725" ref="AL432"/>
-    <hyperlink r:id="rId726" ref="K433"/>
-    <hyperlink r:id="rId727" ref="AJ433"/>
-    <hyperlink r:id="rId728" ref="K434"/>
-    <hyperlink r:id="rId729" ref="AG434"/>
-    <hyperlink r:id="rId730" ref="AJ434"/>
-    <hyperlink r:id="rId731" ref="K435"/>
-    <hyperlink r:id="rId732" ref="AJ435"/>
-    <hyperlink r:id="rId733" ref="K436"/>
-    <hyperlink r:id="rId734" ref="AJ436"/>
-    <hyperlink r:id="rId735" ref="K437"/>
-    <hyperlink r:id="rId736" ref="AJ437"/>
-    <hyperlink r:id="rId737" ref="K438"/>
-    <hyperlink r:id="rId738" ref="AJ438"/>
-    <hyperlink r:id="rId739" ref="K439"/>
-    <hyperlink r:id="rId740" ref="AJ439"/>
-    <hyperlink r:id="rId741" ref="K440"/>
-    <hyperlink r:id="rId742" ref="AJ440"/>
-    <hyperlink r:id="rId743" ref="K441"/>
-    <hyperlink r:id="rId744" ref="AJ441"/>
-    <hyperlink r:id="rId745" ref="K442"/>
-    <hyperlink r:id="rId746" ref="K443"/>
-    <hyperlink r:id="rId747" ref="AJ443"/>
-    <hyperlink r:id="rId748" ref="K444"/>
-    <hyperlink r:id="rId749" ref="AJ444"/>
-    <hyperlink r:id="rId750" ref="K445"/>
-    <hyperlink r:id="rId751" ref="AJ445"/>
-    <hyperlink r:id="rId752" ref="AJ446"/>
-    <hyperlink r:id="rId753" ref="K447"/>
-    <hyperlink r:id="rId754" ref="AJ447"/>
-    <hyperlink r:id="rId755" ref="K448"/>
-    <hyperlink r:id="rId756" ref="AJ448"/>
-    <hyperlink r:id="rId757" ref="K449"/>
-    <hyperlink r:id="rId758" ref="AJ449"/>
-    <hyperlink r:id="rId759" ref="K450"/>
-    <hyperlink r:id="rId760" ref="AJ450"/>
-    <hyperlink r:id="rId761" ref="K452"/>
-    <hyperlink r:id="rId762" ref="AJ452"/>
-    <hyperlink r:id="rId763" ref="K453"/>
-    <hyperlink r:id="rId764" ref="K454"/>
-    <hyperlink r:id="rId765" ref="AA454"/>
-    <hyperlink r:id="rId766" ref="K455"/>
-    <hyperlink r:id="rId767" ref="AJ455"/>
-    <hyperlink r:id="rId768" ref="K456"/>
-    <hyperlink r:id="rId769" ref="AJ456"/>
-    <hyperlink r:id="rId770" ref="K457"/>
-    <hyperlink r:id="rId771" ref="AG457"/>
-    <hyperlink r:id="rId772" ref="AJ457"/>
-    <hyperlink r:id="rId773" ref="K458"/>
-    <hyperlink r:id="rId774" ref="AG458"/>
-    <hyperlink r:id="rId775" ref="AJ458"/>
-    <hyperlink r:id="rId776" ref="K459"/>
-    <hyperlink r:id="rId777" ref="AJ459"/>
-    <hyperlink r:id="rId778" ref="K460"/>
-    <hyperlink r:id="rId779" ref="AJ460"/>
-    <hyperlink r:id="rId780" ref="K461"/>
-    <hyperlink r:id="rId781" ref="AJ461"/>
-    <hyperlink r:id="rId782" ref="K462"/>
-    <hyperlink r:id="rId783" ref="AJ462"/>
-    <hyperlink r:id="rId784" ref="K463"/>
-    <hyperlink r:id="rId785" ref="Y463"/>
-    <hyperlink r:id="rId786" ref="AJ463"/>
-    <hyperlink r:id="rId787" ref="K464"/>
-    <hyperlink r:id="rId788" ref="AJ464"/>
-    <hyperlink r:id="rId789" ref="K465"/>
-    <hyperlink r:id="rId790" ref="AJ465"/>
-    <hyperlink r:id="rId791" ref="K466"/>
-    <hyperlink r:id="rId792" ref="AJ466"/>
-    <hyperlink r:id="rId793" ref="K468"/>
-    <hyperlink r:id="rId794" ref="AG468"/>
-    <hyperlink r:id="rId795" ref="AJ468"/>
-    <hyperlink r:id="rId796" ref="K469"/>
-    <hyperlink r:id="rId797" ref="AJ469"/>
-    <hyperlink r:id="rId798" ref="AT469"/>
-    <hyperlink r:id="rId799" ref="K470"/>
-    <hyperlink r:id="rId800" ref="AJ470"/>
-    <hyperlink r:id="rId801" ref="K471"/>
-    <hyperlink r:id="rId802" ref="AJ471"/>
-    <hyperlink r:id="rId803" ref="K473"/>
-    <hyperlink r:id="rId804" ref="K475"/>
-    <hyperlink r:id="rId805" ref="AJ475"/>
-    <hyperlink r:id="rId806" ref="K477"/>
-    <hyperlink r:id="rId807" ref="AJ477"/>
-    <hyperlink r:id="rId808" ref="K478"/>
-    <hyperlink r:id="rId809" ref="Y478"/>
-    <hyperlink r:id="rId810" ref="AJ478"/>
-    <hyperlink r:id="rId811" ref="K479"/>
-    <hyperlink r:id="rId812" ref="AJ479"/>
-    <hyperlink r:id="rId813" ref="K480"/>
-    <hyperlink r:id="rId814" ref="AJ480"/>
-    <hyperlink r:id="rId815" ref="K481"/>
-    <hyperlink r:id="rId816" ref="AJ481"/>
-    <hyperlink r:id="rId817" ref="K482"/>
-    <hyperlink r:id="rId818" ref="AJ482"/>
-    <hyperlink r:id="rId819" ref="AK483"/>
-    <hyperlink r:id="rId820" ref="K484"/>
-    <hyperlink r:id="rId821" ref="K485"/>
-    <hyperlink r:id="rId822" ref="AJ485"/>
-    <hyperlink r:id="rId823" ref="K486"/>
-    <hyperlink r:id="rId824" ref="AJ486"/>
-    <hyperlink r:id="rId825" ref="K487"/>
-    <hyperlink r:id="rId826" ref="AJ487"/>
-    <hyperlink r:id="rId827" ref="K488"/>
-    <hyperlink r:id="rId828" ref="AJ488"/>
-    <hyperlink r:id="rId829" ref="K489"/>
-    <hyperlink r:id="rId830" ref="AK489"/>
-    <hyperlink r:id="rId831" ref="K490"/>
-    <hyperlink r:id="rId832" ref="AJ490"/>
-    <hyperlink r:id="rId833" ref="K491"/>
-    <hyperlink r:id="rId834" ref="AJ491"/>
-    <hyperlink r:id="rId835" ref="K492"/>
-    <hyperlink r:id="rId836" ref="AJ492"/>
-    <hyperlink r:id="rId837" ref="K493"/>
-    <hyperlink r:id="rId838" ref="AJ493"/>
-    <hyperlink r:id="rId839" ref="K494"/>
-    <hyperlink r:id="rId840" ref="K495"/>
-    <hyperlink r:id="rId841" ref="AJ495"/>
-    <hyperlink r:id="rId842" ref="K496"/>
-    <hyperlink r:id="rId843" ref="AJ496"/>
-    <hyperlink r:id="rId844" ref="K497"/>
-    <hyperlink r:id="rId845" ref="AJ497"/>
-    <hyperlink r:id="rId846" ref="AT499"/>
-    <hyperlink r:id="rId847" ref="K500"/>
-    <hyperlink r:id="rId848" ref="AJ500"/>
-    <hyperlink r:id="rId849" ref="K501"/>
-    <hyperlink r:id="rId850" ref="AJ501"/>
-    <hyperlink r:id="rId851" ref="K502"/>
-    <hyperlink r:id="rId852" ref="AJ502"/>
-    <hyperlink r:id="rId853" ref="K503"/>
-    <hyperlink r:id="rId854" ref="Y503"/>
-    <hyperlink r:id="rId855" ref="AJ503"/>
-    <hyperlink r:id="rId856" ref="K504"/>
-    <hyperlink r:id="rId857" ref="AJ504"/>
-    <hyperlink r:id="rId858" ref="K505"/>
-    <hyperlink r:id="rId859" ref="AJ505"/>
-    <hyperlink r:id="rId860" ref="K506"/>
-    <hyperlink r:id="rId861" ref="AJ506"/>
-    <hyperlink r:id="rId862" ref="K507"/>
-    <hyperlink r:id="rId863" ref="AJ507"/>
-    <hyperlink r:id="rId864" ref="K508"/>
-    <hyperlink r:id="rId865" ref="AJ508"/>
-    <hyperlink r:id="rId866" ref="K509"/>
-    <hyperlink r:id="rId867" ref="AJ509"/>
-    <hyperlink r:id="rId868" ref="AT509"/>
-    <hyperlink r:id="rId869" ref="K510"/>
-    <hyperlink r:id="rId870" ref="AJ510"/>
-    <hyperlink r:id="rId871" ref="K511"/>
-    <hyperlink r:id="rId872" ref="AJ511"/>
-    <hyperlink r:id="rId873" ref="K512"/>
-    <hyperlink r:id="rId874" ref="AJ512"/>
-    <hyperlink r:id="rId875" ref="K513"/>
-    <hyperlink r:id="rId876" ref="AJ513"/>
-    <hyperlink r:id="rId877" ref="K514"/>
-    <hyperlink r:id="rId878" ref="Y514"/>
-    <hyperlink r:id="rId879" ref="AJ514"/>
-    <hyperlink r:id="rId880" ref="K515"/>
-    <hyperlink r:id="rId881" ref="Y515"/>
-    <hyperlink r:id="rId882" ref="AJ515"/>
-    <hyperlink r:id="rId883" ref="K516"/>
-    <hyperlink r:id="rId884" ref="AJ516"/>
-    <hyperlink r:id="rId885" ref="K517"/>
-    <hyperlink r:id="rId886" ref="AJ517"/>
-    <hyperlink r:id="rId887" ref="K518"/>
-    <hyperlink r:id="rId888" ref="AJ518"/>
-    <hyperlink r:id="rId889" ref="K519"/>
-    <hyperlink r:id="rId890" ref="AJ519"/>
-    <hyperlink r:id="rId891" ref="AT519"/>
-    <hyperlink r:id="rId892" ref="K520"/>
-    <hyperlink r:id="rId893" ref="AT520"/>
-    <hyperlink r:id="rId894" ref="K521"/>
-    <hyperlink r:id="rId895" ref="AJ521"/>
-    <hyperlink r:id="rId896" ref="AT521"/>
-    <hyperlink r:id="rId897" ref="AJ522"/>
-    <hyperlink r:id="rId898" ref="K523"/>
-    <hyperlink r:id="rId899" ref="AJ523"/>
-    <hyperlink r:id="rId900" ref="K525"/>
-    <hyperlink r:id="rId901" ref="AJ525"/>
-    <hyperlink r:id="rId902" ref="K526"/>
-    <hyperlink r:id="rId903" ref="AJ526"/>
-    <hyperlink r:id="rId904" ref="K528"/>
-    <hyperlink r:id="rId905" ref="AJ528"/>
-    <hyperlink r:id="rId906" ref="K529"/>
-    <hyperlink r:id="rId907" ref="AJ529"/>
-    <hyperlink r:id="rId908" ref="AT532"/>
-    <hyperlink r:id="rId909" ref="K533"/>
-    <hyperlink r:id="rId910" ref="AJ533"/>
-    <hyperlink r:id="rId911" ref="K534"/>
-    <hyperlink r:id="rId912" ref="AJ534"/>
-    <hyperlink r:id="rId913" ref="K535"/>
-    <hyperlink r:id="rId914" ref="AJ535"/>
-    <hyperlink r:id="rId915" ref="K536"/>
-    <hyperlink r:id="rId916" ref="AJ536"/>
-    <hyperlink r:id="rId917" ref="K537"/>
-    <hyperlink r:id="rId918" ref="AJ537"/>
-    <hyperlink r:id="rId919" ref="K538"/>
-    <hyperlink r:id="rId920" ref="AJ538"/>
-    <hyperlink r:id="rId921" ref="K539"/>
-    <hyperlink r:id="rId922" ref="AJ539"/>
-    <hyperlink r:id="rId923" ref="K540"/>
-    <hyperlink r:id="rId924" ref="AK540"/>
-    <hyperlink r:id="rId925" ref="K541"/>
-    <hyperlink r:id="rId926" ref="AJ541"/>
-    <hyperlink r:id="rId927" ref="K542"/>
-    <hyperlink r:id="rId928" ref="AJ542"/>
-    <hyperlink r:id="rId929" ref="K543"/>
-    <hyperlink r:id="rId930" ref="AJ543"/>
-    <hyperlink r:id="rId931" ref="K544"/>
-    <hyperlink r:id="rId932" ref="AJ544"/>
-    <hyperlink r:id="rId933" ref="K545"/>
-    <hyperlink r:id="rId934" ref="AJ545"/>
-    <hyperlink r:id="rId935" ref="K546"/>
-    <hyperlink r:id="rId936" ref="AJ546"/>
-    <hyperlink r:id="rId937" ref="AT546"/>
-    <hyperlink r:id="rId938" ref="K547"/>
-    <hyperlink r:id="rId939" ref="Y547"/>
-    <hyperlink r:id="rId940" ref="AJ547"/>
-    <hyperlink r:id="rId941" ref="K548"/>
-    <hyperlink r:id="rId942" ref="AJ548"/>
+    <hyperlink r:id="rId205" ref="Y126"/>
+    <hyperlink r:id="rId206" ref="AJ126"/>
+    <hyperlink r:id="rId207" ref="AJ127"/>
+    <hyperlink r:id="rId208" ref="K128"/>
+    <hyperlink r:id="rId209" ref="AJ128"/>
+    <hyperlink r:id="rId210" ref="K130"/>
+    <hyperlink r:id="rId211" ref="AJ130"/>
+    <hyperlink r:id="rId212" ref="K131"/>
+    <hyperlink r:id="rId213" ref="AJ131"/>
+    <hyperlink r:id="rId214" ref="K132"/>
+    <hyperlink r:id="rId215" ref="K133"/>
+    <hyperlink r:id="rId216" ref="AJ133"/>
+    <hyperlink r:id="rId217" ref="K134"/>
+    <hyperlink r:id="rId218" ref="AJ134"/>
+    <hyperlink r:id="rId219" ref="K135"/>
+    <hyperlink r:id="rId220" ref="AJ135"/>
+    <hyperlink r:id="rId221" ref="K136"/>
+    <hyperlink r:id="rId222" ref="AJ136"/>
+    <hyperlink r:id="rId223" ref="K137"/>
+    <hyperlink r:id="rId224" ref="AJ137"/>
+    <hyperlink r:id="rId225" ref="K138"/>
+    <hyperlink r:id="rId226" ref="K139"/>
+    <hyperlink r:id="rId227" ref="AJ139"/>
+    <hyperlink r:id="rId228" ref="K140"/>
+    <hyperlink r:id="rId229" ref="AJ140"/>
+    <hyperlink r:id="rId230" ref="K141"/>
+    <hyperlink r:id="rId231" ref="AK141"/>
+    <hyperlink r:id="rId232" ref="K142"/>
+    <hyperlink r:id="rId233" ref="AK142"/>
+    <hyperlink r:id="rId234" ref="K143"/>
+    <hyperlink r:id="rId235" ref="AK143"/>
+    <hyperlink r:id="rId236" ref="K144"/>
+    <hyperlink r:id="rId237" ref="AK144"/>
+    <hyperlink r:id="rId238" ref="K145"/>
+    <hyperlink r:id="rId239" ref="AK145"/>
+    <hyperlink r:id="rId240" ref="K146"/>
+    <hyperlink r:id="rId241" ref="AJ146"/>
+    <hyperlink r:id="rId242" ref="K147"/>
+    <hyperlink r:id="rId243" ref="AJ147"/>
+    <hyperlink r:id="rId244" ref="K148"/>
+    <hyperlink r:id="rId245" ref="AJ148"/>
+    <hyperlink r:id="rId246" ref="K149"/>
+    <hyperlink r:id="rId247" ref="AJ149"/>
+    <hyperlink r:id="rId248" ref="K150"/>
+    <hyperlink r:id="rId249" ref="AJ150"/>
+    <hyperlink r:id="rId250" ref="K151"/>
+    <hyperlink r:id="rId251" ref="AJ151"/>
+    <hyperlink r:id="rId252" ref="K152"/>
+    <hyperlink r:id="rId253" ref="AJ152"/>
+    <hyperlink r:id="rId254" ref="K153"/>
+    <hyperlink r:id="rId255" ref="AJ153"/>
+    <hyperlink r:id="rId256" ref="K154"/>
+    <hyperlink r:id="rId257" ref="AJ154"/>
+    <hyperlink r:id="rId258" ref="K155"/>
+    <hyperlink r:id="rId259" ref="AJ155"/>
+    <hyperlink r:id="rId260" ref="K156"/>
+    <hyperlink r:id="rId261" ref="AJ156"/>
+    <hyperlink r:id="rId262" ref="K157"/>
+    <hyperlink r:id="rId263" ref="AJ157"/>
+    <hyperlink r:id="rId264" ref="K158"/>
+    <hyperlink r:id="rId265" ref="AJ158"/>
+    <hyperlink r:id="rId266" ref="K162"/>
+    <hyperlink r:id="rId267" ref="AJ162"/>
+    <hyperlink r:id="rId268" ref="K165"/>
+    <hyperlink r:id="rId269" ref="AJ165"/>
+    <hyperlink r:id="rId270" ref="K166"/>
+    <hyperlink r:id="rId271" ref="K167"/>
+    <hyperlink r:id="rId272" ref="K170"/>
+    <hyperlink r:id="rId273" ref="AK170"/>
+    <hyperlink r:id="rId274" ref="K171"/>
+    <hyperlink r:id="rId275" ref="Y171"/>
+    <hyperlink r:id="rId276" ref="K172"/>
+    <hyperlink r:id="rId277" ref="AK172"/>
+    <hyperlink r:id="rId278" ref="K173"/>
+    <hyperlink r:id="rId279" ref="AJ173"/>
+    <hyperlink r:id="rId280" ref="K176"/>
+    <hyperlink r:id="rId281" ref="AJ176"/>
+    <hyperlink r:id="rId282" ref="K177"/>
+    <hyperlink r:id="rId283" ref="AJ177"/>
+    <hyperlink r:id="rId284" ref="K178"/>
+    <hyperlink r:id="rId285" ref="AG178"/>
+    <hyperlink r:id="rId286" ref="AJ178"/>
+    <hyperlink r:id="rId287" ref="K179"/>
+    <hyperlink r:id="rId288" ref="K180"/>
+    <hyperlink r:id="rId289" ref="AJ180"/>
+    <hyperlink r:id="rId290" ref="K184"/>
+    <hyperlink r:id="rId291" ref="AJ184"/>
+    <hyperlink r:id="rId292" ref="K185"/>
+    <hyperlink r:id="rId293" ref="AJ185"/>
+    <hyperlink r:id="rId294" ref="K187"/>
+    <hyperlink r:id="rId295" ref="AJ187"/>
+    <hyperlink r:id="rId296" ref="AJ188"/>
+    <hyperlink r:id="rId297" ref="K189"/>
+    <hyperlink r:id="rId298" ref="K190"/>
+    <hyperlink r:id="rId299" ref="AJ190"/>
+    <hyperlink r:id="rId300" ref="K191"/>
+    <hyperlink r:id="rId301" ref="AJ191"/>
+    <hyperlink r:id="rId302" ref="K192"/>
+    <hyperlink r:id="rId303" ref="AJ192"/>
+    <hyperlink r:id="rId304" ref="K193"/>
+    <hyperlink r:id="rId305" ref="AJ193"/>
+    <hyperlink r:id="rId306" ref="AJ194"/>
+    <hyperlink r:id="rId307" ref="AT194"/>
+    <hyperlink r:id="rId308" ref="AT195"/>
+    <hyperlink r:id="rId309" ref="K196"/>
+    <hyperlink r:id="rId310" ref="AK196"/>
+    <hyperlink r:id="rId311" ref="K197"/>
+    <hyperlink r:id="rId312" ref="AJ197"/>
+    <hyperlink r:id="rId313" ref="K198"/>
+    <hyperlink r:id="rId314" ref="AJ198"/>
+    <hyperlink r:id="rId315" ref="K199"/>
+    <hyperlink r:id="rId316" ref="AJ199"/>
+    <hyperlink r:id="rId317" ref="K200"/>
+    <hyperlink r:id="rId318" ref="AJ200"/>
+    <hyperlink r:id="rId319" ref="K201"/>
+    <hyperlink r:id="rId320" ref="AJ201"/>
+    <hyperlink r:id="rId321" ref="K202"/>
+    <hyperlink r:id="rId322" ref="Y202"/>
+    <hyperlink r:id="rId323" ref="AJ202"/>
+    <hyperlink r:id="rId324" ref="K203"/>
+    <hyperlink r:id="rId325" ref="AJ203"/>
+    <hyperlink r:id="rId326" ref="K204"/>
+    <hyperlink r:id="rId327" ref="Y204"/>
+    <hyperlink r:id="rId328" ref="AJ204"/>
+    <hyperlink r:id="rId329" ref="K205"/>
+    <hyperlink r:id="rId330" ref="AJ205"/>
+    <hyperlink r:id="rId331" ref="K206"/>
+    <hyperlink r:id="rId332" ref="AJ206"/>
+    <hyperlink r:id="rId333" ref="K207"/>
+    <hyperlink r:id="rId334" ref="AJ207"/>
+    <hyperlink r:id="rId335" ref="K208"/>
+    <hyperlink r:id="rId336" ref="AJ208"/>
+    <hyperlink r:id="rId337" ref="K209"/>
+    <hyperlink r:id="rId338" ref="AJ209"/>
+    <hyperlink r:id="rId339" ref="K210"/>
+    <hyperlink r:id="rId340" ref="AJ210"/>
+    <hyperlink r:id="rId341" ref="K211"/>
+    <hyperlink r:id="rId342" ref="AJ211"/>
+    <hyperlink r:id="rId343" ref="AJ212"/>
+    <hyperlink r:id="rId344" ref="K213"/>
+    <hyperlink r:id="rId345" ref="AT214"/>
+    <hyperlink r:id="rId346" ref="K215"/>
+    <hyperlink r:id="rId347" ref="AJ215"/>
+    <hyperlink r:id="rId348" ref="K216"/>
+    <hyperlink r:id="rId349" ref="AJ216"/>
+    <hyperlink r:id="rId350" location="v=onepage&amp;q&amp;f=false" ref="AT216"/>
+    <hyperlink r:id="rId351" ref="K217"/>
+    <hyperlink r:id="rId352" ref="AJ217"/>
+    <hyperlink r:id="rId353" ref="AL217"/>
+    <hyperlink r:id="rId354" ref="AO217"/>
+    <hyperlink r:id="rId355" ref="AJ218"/>
+    <hyperlink r:id="rId356" ref="AM218"/>
+    <hyperlink r:id="rId357" location="v=onepage&amp;q&amp;f=false" ref="AT218"/>
+    <hyperlink r:id="rId358" ref="K219"/>
+    <hyperlink r:id="rId359" ref="AK219"/>
+    <hyperlink r:id="rId360" ref="K220"/>
+    <hyperlink r:id="rId361" ref="AJ220"/>
+    <hyperlink r:id="rId362" ref="K221"/>
+    <hyperlink r:id="rId363" ref="AJ221"/>
+    <hyperlink r:id="rId364" ref="K222"/>
+    <hyperlink r:id="rId365" ref="AJ222"/>
+    <hyperlink r:id="rId366" ref="K223"/>
+    <hyperlink r:id="rId367" ref="AJ223"/>
+    <hyperlink r:id="rId368" ref="K224"/>
+    <hyperlink r:id="rId369" ref="AJ224"/>
+    <hyperlink r:id="rId370" ref="K226"/>
+    <hyperlink r:id="rId371" ref="AJ226"/>
+    <hyperlink r:id="rId372" ref="K227"/>
+    <hyperlink r:id="rId373" ref="AJ227"/>
+    <hyperlink r:id="rId374" ref="K228"/>
+    <hyperlink r:id="rId375" ref="K229"/>
+    <hyperlink r:id="rId376" ref="AJ229"/>
+    <hyperlink r:id="rId377" ref="K231"/>
+    <hyperlink r:id="rId378" ref="AJ231"/>
+    <hyperlink r:id="rId379" ref="K233"/>
+    <hyperlink r:id="rId380" ref="AJ233"/>
+    <hyperlink r:id="rId381" ref="K235"/>
+    <hyperlink r:id="rId382" ref="AJ235"/>
+    <hyperlink r:id="rId383" ref="K236"/>
+    <hyperlink r:id="rId384" ref="AJ236"/>
+    <hyperlink r:id="rId385" ref="AT237"/>
+    <hyperlink r:id="rId386" ref="K238"/>
+    <hyperlink r:id="rId387" ref="AJ238"/>
+    <hyperlink r:id="rId388" ref="K239"/>
+    <hyperlink r:id="rId389" ref="AJ239"/>
+    <hyperlink r:id="rId390" ref="K240"/>
+    <hyperlink r:id="rId391" ref="AL240"/>
+    <hyperlink r:id="rId392" ref="K241"/>
+    <hyperlink r:id="rId393" ref="AJ241"/>
+    <hyperlink r:id="rId394" ref="K242"/>
+    <hyperlink r:id="rId395" ref="AJ242"/>
+    <hyperlink r:id="rId396" ref="K245"/>
+    <hyperlink r:id="rId397" ref="K246"/>
+    <hyperlink r:id="rId398" ref="AJ246"/>
+    <hyperlink r:id="rId399" ref="K247"/>
+    <hyperlink r:id="rId400" ref="AJ247"/>
+    <hyperlink r:id="rId401" ref="K249"/>
+    <hyperlink r:id="rId402" ref="AJ249"/>
+    <hyperlink r:id="rId403" ref="K250"/>
+    <hyperlink r:id="rId404" ref="K252"/>
+    <hyperlink r:id="rId405" ref="AJ252"/>
+    <hyperlink r:id="rId406" ref="K253"/>
+    <hyperlink r:id="rId407" ref="AK253"/>
+    <hyperlink r:id="rId408" ref="AT253"/>
+    <hyperlink r:id="rId409" ref="K254"/>
+    <hyperlink r:id="rId410" ref="AJ254"/>
+    <hyperlink r:id="rId411" ref="K255"/>
+    <hyperlink r:id="rId412" ref="AJ255"/>
+    <hyperlink r:id="rId413" ref="AJ256"/>
+    <hyperlink r:id="rId414" ref="K259"/>
+    <hyperlink r:id="rId415" ref="AJ259"/>
+    <hyperlink r:id="rId416" ref="K260"/>
+    <hyperlink r:id="rId417" ref="AJ260"/>
+    <hyperlink r:id="rId418" ref="K261"/>
+    <hyperlink r:id="rId419" ref="AJ261"/>
+    <hyperlink r:id="rId420" ref="K262"/>
+    <hyperlink r:id="rId421" ref="AJ262"/>
+    <hyperlink r:id="rId422" ref="K263"/>
+    <hyperlink r:id="rId423" ref="AJ263"/>
+    <hyperlink r:id="rId424" ref="K264"/>
+    <hyperlink r:id="rId425" ref="Y264"/>
+    <hyperlink r:id="rId426" ref="AJ264"/>
+    <hyperlink r:id="rId427" ref="K265"/>
+    <hyperlink r:id="rId428" ref="AJ265"/>
+    <hyperlink r:id="rId429" ref="K266"/>
+    <hyperlink r:id="rId430" ref="AJ266"/>
+    <hyperlink r:id="rId431" ref="K267"/>
+    <hyperlink r:id="rId432" ref="AJ267"/>
+    <hyperlink r:id="rId433" ref="K268"/>
+    <hyperlink r:id="rId434" ref="AJ268"/>
+    <hyperlink r:id="rId435" ref="K269"/>
+    <hyperlink r:id="rId436" ref="AJ269"/>
+    <hyperlink r:id="rId437" ref="K271"/>
+    <hyperlink r:id="rId438" ref="AJ271"/>
+    <hyperlink r:id="rId439" location="v=onepage&amp;q=%22Deutschen%20Evangelischen%20Synode%20von%20S%C3%BCdwestafrika%22&amp;f=false" ref="AT271"/>
+    <hyperlink r:id="rId440" ref="K272"/>
+    <hyperlink r:id="rId441" ref="AK272"/>
+    <hyperlink r:id="rId442" ref="K273"/>
+    <hyperlink r:id="rId443" ref="AJ273"/>
+    <hyperlink r:id="rId444" ref="AT274"/>
+    <hyperlink r:id="rId445" ref="K275"/>
+    <hyperlink r:id="rId446" ref="AJ275"/>
+    <hyperlink r:id="rId447" ref="K276"/>
+    <hyperlink r:id="rId448" ref="AJ276"/>
+    <hyperlink r:id="rId449" ref="K277"/>
+    <hyperlink r:id="rId450" ref="AJ277"/>
+    <hyperlink r:id="rId451" ref="K278"/>
+    <hyperlink r:id="rId452" ref="AJ278"/>
+    <hyperlink r:id="rId453" ref="K279"/>
+    <hyperlink r:id="rId454" ref="AJ279"/>
+    <hyperlink r:id="rId455" ref="K280"/>
+    <hyperlink r:id="rId456" ref="AJ280"/>
+    <hyperlink r:id="rId457" ref="AJ281"/>
+    <hyperlink r:id="rId458" ref="K282"/>
+    <hyperlink r:id="rId459" ref="AJ282"/>
+    <hyperlink r:id="rId460" ref="K283"/>
+    <hyperlink r:id="rId461" ref="AJ283"/>
+    <hyperlink r:id="rId462" ref="K284"/>
+    <hyperlink r:id="rId463" ref="AJ284"/>
+    <hyperlink r:id="rId464" ref="K285"/>
+    <hyperlink r:id="rId465" ref="Y285"/>
+    <hyperlink r:id="rId466" ref="AA285"/>
+    <hyperlink r:id="rId467" ref="K286"/>
+    <hyperlink r:id="rId468" ref="AJ286"/>
+    <hyperlink r:id="rId469" ref="K287"/>
+    <hyperlink r:id="rId470" ref="AJ287"/>
+    <hyperlink r:id="rId471" ref="AT287"/>
+    <hyperlink r:id="rId472" ref="K288"/>
+    <hyperlink r:id="rId473" ref="AJ288"/>
+    <hyperlink r:id="rId474" ref="K289"/>
+    <hyperlink r:id="rId475" ref="AJ289"/>
+    <hyperlink r:id="rId476" ref="K290"/>
+    <hyperlink r:id="rId477" ref="AJ290"/>
+    <hyperlink r:id="rId478" ref="K291"/>
+    <hyperlink r:id="rId479" ref="AJ291"/>
+    <hyperlink r:id="rId480" ref="K292"/>
+    <hyperlink r:id="rId481" ref="AJ292"/>
+    <hyperlink r:id="rId482" ref="K293"/>
+    <hyperlink r:id="rId483" ref="AA293"/>
+    <hyperlink r:id="rId484" ref="AC293"/>
+    <hyperlink r:id="rId485" ref="AJ293"/>
+    <hyperlink r:id="rId486" ref="AK293"/>
+    <hyperlink r:id="rId487" ref="K296"/>
+    <hyperlink r:id="rId488" ref="AJ296"/>
+    <hyperlink r:id="rId489" ref="K297"/>
+    <hyperlink r:id="rId490" ref="AJ297"/>
+    <hyperlink r:id="rId491" ref="K298"/>
+    <hyperlink r:id="rId492" ref="K299"/>
+    <hyperlink r:id="rId493" ref="AJ299"/>
+    <hyperlink r:id="rId494" ref="K300"/>
+    <hyperlink r:id="rId495" ref="AJ300"/>
+    <hyperlink r:id="rId496" ref="K301"/>
+    <hyperlink r:id="rId497" ref="K302"/>
+    <hyperlink r:id="rId498" ref="Y302"/>
+    <hyperlink r:id="rId499" ref="AK302"/>
+    <hyperlink r:id="rId500" ref="K303"/>
+    <hyperlink r:id="rId501" ref="Y303"/>
+    <hyperlink r:id="rId502" ref="K304"/>
+    <hyperlink r:id="rId503" ref="AJ304"/>
+    <hyperlink r:id="rId504" ref="K305"/>
+    <hyperlink r:id="rId505" ref="AK305"/>
+    <hyperlink r:id="rId506" ref="K306"/>
+    <hyperlink r:id="rId507" ref="AJ306"/>
+    <hyperlink r:id="rId508" ref="K307"/>
+    <hyperlink r:id="rId509" ref="AJ307"/>
+    <hyperlink r:id="rId510" ref="K308"/>
+    <hyperlink r:id="rId511" ref="AJ308"/>
+    <hyperlink r:id="rId512" ref="K309"/>
+    <hyperlink r:id="rId513" ref="K310"/>
+    <hyperlink r:id="rId514" ref="AJ310"/>
+    <hyperlink r:id="rId515" ref="K311"/>
+    <hyperlink r:id="rId516" ref="AL311"/>
+    <hyperlink r:id="rId517" ref="K313"/>
+    <hyperlink r:id="rId518" ref="AJ313"/>
+    <hyperlink r:id="rId519" ref="K314"/>
+    <hyperlink r:id="rId520" ref="Y314"/>
+    <hyperlink r:id="rId521" ref="AJ314"/>
+    <hyperlink r:id="rId522" ref="K315"/>
+    <hyperlink r:id="rId523" ref="AJ315"/>
+    <hyperlink r:id="rId524" ref="K316"/>
+    <hyperlink r:id="rId525" ref="AJ316"/>
+    <hyperlink r:id="rId526" ref="K317"/>
+    <hyperlink r:id="rId527" ref="AJ317"/>
+    <hyperlink r:id="rId528" ref="AL318"/>
+    <hyperlink r:id="rId529" ref="K319"/>
+    <hyperlink r:id="rId530" ref="AL319"/>
+    <hyperlink r:id="rId531" ref="K320"/>
+    <hyperlink r:id="rId532" ref="AJ320"/>
+    <hyperlink r:id="rId533" ref="K321"/>
+    <hyperlink r:id="rId534" ref="AJ321"/>
+    <hyperlink r:id="rId535" ref="K322"/>
+    <hyperlink r:id="rId536" ref="AJ322"/>
+    <hyperlink r:id="rId537" ref="K323"/>
+    <hyperlink r:id="rId538" ref="AL323"/>
+    <hyperlink r:id="rId539" ref="K324"/>
+    <hyperlink r:id="rId540" ref="AJ324"/>
+    <hyperlink r:id="rId541" ref="K325"/>
+    <hyperlink r:id="rId542" ref="AJ325"/>
+    <hyperlink r:id="rId543" ref="K326"/>
+    <hyperlink r:id="rId544" ref="AJ326"/>
+    <hyperlink r:id="rId545" ref="K327"/>
+    <hyperlink r:id="rId546" ref="AJ327"/>
+    <hyperlink r:id="rId547" ref="K330"/>
+    <hyperlink r:id="rId548" ref="AJ330"/>
+    <hyperlink r:id="rId549" ref="K331"/>
+    <hyperlink r:id="rId550" ref="AJ331"/>
+    <hyperlink r:id="rId551" ref="K332"/>
+    <hyperlink r:id="rId552" ref="AJ332"/>
+    <hyperlink r:id="rId553" ref="K333"/>
+    <hyperlink r:id="rId554" ref="AJ333"/>
+    <hyperlink r:id="rId555" ref="K334"/>
+    <hyperlink r:id="rId556" ref="AJ334"/>
+    <hyperlink r:id="rId557" ref="K336"/>
+    <hyperlink r:id="rId558" ref="AJ336"/>
+    <hyperlink r:id="rId559" ref="K337"/>
+    <hyperlink r:id="rId560" ref="AJ337"/>
+    <hyperlink r:id="rId561" ref="K338"/>
+    <hyperlink r:id="rId562" ref="AJ338"/>
+    <hyperlink r:id="rId563" ref="K339"/>
+    <hyperlink r:id="rId564" ref="Y339"/>
+    <hyperlink r:id="rId565" ref="AJ339"/>
+    <hyperlink r:id="rId566" ref="K340"/>
+    <hyperlink r:id="rId567" ref="AJ340"/>
+    <hyperlink r:id="rId568" ref="K341"/>
+    <hyperlink r:id="rId569" ref="AJ341"/>
+    <hyperlink r:id="rId570" ref="K342"/>
+    <hyperlink r:id="rId571" ref="AJ342"/>
+    <hyperlink r:id="rId572" ref="K343"/>
+    <hyperlink r:id="rId573" ref="AJ343"/>
+    <hyperlink r:id="rId574" ref="AJ345"/>
+    <hyperlink r:id="rId575" ref="K347"/>
+    <hyperlink r:id="rId576" ref="K348"/>
+    <hyperlink r:id="rId577" ref="K352"/>
+    <hyperlink r:id="rId578" ref="K353"/>
+    <hyperlink r:id="rId579" ref="AJ353"/>
+    <hyperlink r:id="rId580" ref="K354"/>
+    <hyperlink r:id="rId581" ref="AJ354"/>
+    <hyperlink r:id="rId582" ref="K355"/>
+    <hyperlink r:id="rId583" ref="AJ355"/>
+    <hyperlink r:id="rId584" ref="AJ356"/>
+    <hyperlink r:id="rId585" ref="K357"/>
+    <hyperlink r:id="rId586" ref="AJ357"/>
+    <hyperlink r:id="rId587" ref="K358"/>
+    <hyperlink r:id="rId588" ref="AJ358"/>
+    <hyperlink r:id="rId589" ref="K359"/>
+    <hyperlink r:id="rId590" ref="AK359"/>
+    <hyperlink r:id="rId591" ref="K360"/>
+    <hyperlink r:id="rId592" ref="AJ360"/>
+    <hyperlink r:id="rId593" ref="K361"/>
+    <hyperlink r:id="rId594" ref="AJ361"/>
+    <hyperlink r:id="rId595" ref="K362"/>
+    <hyperlink r:id="rId596" ref="Y362"/>
+    <hyperlink r:id="rId597" ref="AJ362"/>
+    <hyperlink r:id="rId598" ref="K363"/>
+    <hyperlink r:id="rId599" ref="AJ363"/>
+    <hyperlink r:id="rId600" ref="K364"/>
+    <hyperlink r:id="rId601" ref="AJ364"/>
+    <hyperlink r:id="rId602" ref="K365"/>
+    <hyperlink r:id="rId603" ref="AJ365"/>
+    <hyperlink r:id="rId604" ref="K366"/>
+    <hyperlink r:id="rId605" ref="Y366"/>
+    <hyperlink r:id="rId606" ref="AJ366"/>
+    <hyperlink r:id="rId607" ref="K369"/>
+    <hyperlink r:id="rId608" ref="AJ369"/>
+    <hyperlink r:id="rId609" location="v=onepage&amp;q&amp;f=false" ref="AT369"/>
+    <hyperlink r:id="rId610" ref="K370"/>
+    <hyperlink r:id="rId611" ref="AK370"/>
+    <hyperlink r:id="rId612" location="v=onepage&amp;q&amp;f=false" ref="AT370"/>
+    <hyperlink r:id="rId613" ref="K371"/>
+    <hyperlink r:id="rId614" ref="Y371"/>
+    <hyperlink r:id="rId615" ref="AJ371"/>
+    <hyperlink r:id="rId616" ref="K372"/>
+    <hyperlink r:id="rId617" ref="AJ372"/>
+    <hyperlink r:id="rId618" ref="K373"/>
+    <hyperlink r:id="rId619" ref="AJ373"/>
+    <hyperlink r:id="rId620" ref="K374"/>
+    <hyperlink r:id="rId621" ref="AJ374"/>
+    <hyperlink r:id="rId622" ref="AT374"/>
+    <hyperlink r:id="rId623" ref="K375"/>
+    <hyperlink r:id="rId624" ref="AJ375"/>
+    <hyperlink r:id="rId625" ref="K376"/>
+    <hyperlink r:id="rId626" ref="Y376"/>
+    <hyperlink r:id="rId627" ref="AJ376"/>
+    <hyperlink r:id="rId628" ref="K377"/>
+    <hyperlink r:id="rId629" ref="AJ377"/>
+    <hyperlink r:id="rId630" ref="K378"/>
+    <hyperlink r:id="rId631" ref="AJ378"/>
+    <hyperlink r:id="rId632" ref="K379"/>
+    <hyperlink r:id="rId633" ref="AJ379"/>
+    <hyperlink r:id="rId634" ref="K380"/>
+    <hyperlink r:id="rId635" ref="AJ380"/>
+    <hyperlink r:id="rId636" ref="K381"/>
+    <hyperlink r:id="rId637" ref="AJ381"/>
+    <hyperlink r:id="rId638" ref="K382"/>
+    <hyperlink r:id="rId639" ref="AJ382"/>
+    <hyperlink r:id="rId640" ref="K383"/>
+    <hyperlink r:id="rId641" ref="AJ383"/>
+    <hyperlink r:id="rId642" ref="K384"/>
+    <hyperlink r:id="rId643" ref="AJ384"/>
+    <hyperlink r:id="rId644" ref="K385"/>
+    <hyperlink r:id="rId645" ref="AJ385"/>
+    <hyperlink r:id="rId646" ref="K386"/>
+    <hyperlink r:id="rId647" ref="AJ386"/>
+    <hyperlink r:id="rId648" ref="K387"/>
+    <hyperlink r:id="rId649" ref="AJ387"/>
+    <hyperlink r:id="rId650" ref="K388"/>
+    <hyperlink r:id="rId651" ref="AJ388"/>
+    <hyperlink r:id="rId652" ref="K389"/>
+    <hyperlink r:id="rId653" ref="AJ389"/>
+    <hyperlink r:id="rId654" ref="K390"/>
+    <hyperlink r:id="rId655" ref="AJ390"/>
+    <hyperlink r:id="rId656" ref="K391"/>
+    <hyperlink r:id="rId657" ref="AJ391"/>
+    <hyperlink r:id="rId658" ref="K392"/>
+    <hyperlink r:id="rId659" ref="AJ392"/>
+    <hyperlink r:id="rId660" ref="K393"/>
+    <hyperlink r:id="rId661" ref="Y393"/>
+    <hyperlink r:id="rId662" ref="AA393"/>
+    <hyperlink r:id="rId663" ref="AJ393"/>
+    <hyperlink r:id="rId664" ref="K394"/>
+    <hyperlink r:id="rId665" ref="AJ394"/>
+    <hyperlink r:id="rId666" ref="K395"/>
+    <hyperlink r:id="rId667" ref="AJ395"/>
+    <hyperlink r:id="rId668" ref="K396"/>
+    <hyperlink r:id="rId669" ref="AJ396"/>
+    <hyperlink r:id="rId670" ref="K397"/>
+    <hyperlink r:id="rId671" ref="AJ397"/>
+    <hyperlink r:id="rId672" ref="K398"/>
+    <hyperlink r:id="rId673" ref="AJ398"/>
+    <hyperlink r:id="rId674" ref="K399"/>
+    <hyperlink r:id="rId675" ref="AJ399"/>
+    <hyperlink r:id="rId676" ref="K400"/>
+    <hyperlink r:id="rId677" ref="AJ400"/>
+    <hyperlink r:id="rId678" ref="K401"/>
+    <hyperlink r:id="rId679" ref="AJ401"/>
+    <hyperlink r:id="rId680" ref="K402"/>
+    <hyperlink r:id="rId681" ref="AJ402"/>
+    <hyperlink r:id="rId682" ref="K403"/>
+    <hyperlink r:id="rId683" ref="AJ403"/>
+    <hyperlink r:id="rId684" ref="K404"/>
+    <hyperlink r:id="rId685" ref="AJ404"/>
+    <hyperlink r:id="rId686" ref="K405"/>
+    <hyperlink r:id="rId687" ref="AJ405"/>
+    <hyperlink r:id="rId688" ref="K406"/>
+    <hyperlink r:id="rId689" ref="AJ406"/>
+    <hyperlink r:id="rId690" ref="K407"/>
+    <hyperlink r:id="rId691" ref="AJ407"/>
+    <hyperlink r:id="rId692" ref="K408"/>
+    <hyperlink r:id="rId693" ref="AJ408"/>
+    <hyperlink r:id="rId694" ref="K409"/>
+    <hyperlink r:id="rId695" ref="AJ409"/>
+    <hyperlink r:id="rId696" ref="K410"/>
+    <hyperlink r:id="rId697" ref="AJ410"/>
+    <hyperlink r:id="rId698" ref="K411"/>
+    <hyperlink r:id="rId699" ref="AJ411"/>
+    <hyperlink r:id="rId700" ref="K412"/>
+    <hyperlink r:id="rId701" ref="AJ412"/>
+    <hyperlink r:id="rId702" ref="AJ417"/>
+    <hyperlink r:id="rId703" ref="K418"/>
+    <hyperlink r:id="rId704" ref="AJ418"/>
+    <hyperlink r:id="rId705" ref="K419"/>
+    <hyperlink r:id="rId706" ref="K420"/>
+    <hyperlink r:id="rId707" ref="AJ420"/>
+    <hyperlink r:id="rId708" ref="AJ421"/>
+    <hyperlink r:id="rId709" ref="AK422"/>
+    <hyperlink r:id="rId710" ref="AL422"/>
+    <hyperlink r:id="rId711" ref="K424"/>
+    <hyperlink r:id="rId712" ref="AJ424"/>
+    <hyperlink r:id="rId713" ref="K425"/>
+    <hyperlink r:id="rId714" ref="AJ425"/>
+    <hyperlink r:id="rId715" ref="K426"/>
+    <hyperlink r:id="rId716" ref="AJ426"/>
+    <hyperlink r:id="rId717" ref="K427"/>
+    <hyperlink r:id="rId718" ref="AJ427"/>
+    <hyperlink r:id="rId719" ref="K430"/>
+    <hyperlink r:id="rId720" ref="AJ430"/>
+    <hyperlink r:id="rId721" ref="AK430"/>
+    <hyperlink r:id="rId722" ref="K431"/>
+    <hyperlink r:id="rId723" ref="AJ431"/>
+    <hyperlink r:id="rId724" ref="AL432"/>
+    <hyperlink r:id="rId725" ref="K433"/>
+    <hyperlink r:id="rId726" ref="AJ433"/>
+    <hyperlink r:id="rId727" ref="K434"/>
+    <hyperlink r:id="rId728" ref="AG434"/>
+    <hyperlink r:id="rId729" ref="AJ434"/>
+    <hyperlink r:id="rId730" ref="K435"/>
+    <hyperlink r:id="rId731" ref="AJ435"/>
+    <hyperlink r:id="rId732" ref="K436"/>
+    <hyperlink r:id="rId733" ref="AJ436"/>
+    <hyperlink r:id="rId734" ref="K437"/>
+    <hyperlink r:id="rId735" ref="AJ437"/>
+    <hyperlink r:id="rId736" ref="K438"/>
+    <hyperlink r:id="rId737" ref="AJ438"/>
+    <hyperlink r:id="rId738" ref="K439"/>
+    <hyperlink r:id="rId739" ref="AJ439"/>
+    <hyperlink r:id="rId740" ref="K440"/>
+    <hyperlink r:id="rId741" ref="AJ440"/>
+    <hyperlink r:id="rId742" ref="K441"/>
+    <hyperlink r:id="rId743" ref="AJ441"/>
+    <hyperlink r:id="rId744" ref="K442"/>
+    <hyperlink r:id="rId745" ref="K443"/>
+    <hyperlink r:id="rId746" ref="AJ443"/>
+    <hyperlink r:id="rId747" ref="K444"/>
+    <hyperlink r:id="rId748" ref="AJ444"/>
+    <hyperlink r:id="rId749" ref="K445"/>
+    <hyperlink r:id="rId750" ref="AJ445"/>
+    <hyperlink r:id="rId751" ref="AJ446"/>
+    <hyperlink r:id="rId752" ref="K447"/>
+    <hyperlink r:id="rId753" ref="AJ447"/>
+    <hyperlink r:id="rId754" ref="K448"/>
+    <hyperlink r:id="rId755" ref="AJ448"/>
+    <hyperlink r:id="rId756" ref="K449"/>
+    <hyperlink r:id="rId757" ref="AJ449"/>
+    <hyperlink r:id="rId758" ref="K450"/>
+    <hyperlink r:id="rId759" ref="AJ450"/>
+    <hyperlink r:id="rId760" ref="K452"/>
+    <hyperlink r:id="rId761" ref="AJ452"/>
+    <hyperlink r:id="rId762" ref="K453"/>
+    <hyperlink r:id="rId763" ref="K454"/>
+    <hyperlink r:id="rId764" ref="AA454"/>
+    <hyperlink r:id="rId765" ref="K455"/>
+    <hyperlink r:id="rId766" ref="AJ455"/>
+    <hyperlink r:id="rId767" ref="K456"/>
+    <hyperlink r:id="rId768" ref="AJ456"/>
+    <hyperlink r:id="rId769" ref="K457"/>
+    <hyperlink r:id="rId770" ref="AG457"/>
+    <hyperlink r:id="rId771" ref="AJ457"/>
+    <hyperlink r:id="rId772" ref="K458"/>
+    <hyperlink r:id="rId773" ref="AG458"/>
+    <hyperlink r:id="rId774" ref="AJ458"/>
+    <hyperlink r:id="rId775" ref="K459"/>
+    <hyperlink r:id="rId776" ref="AJ459"/>
+    <hyperlink r:id="rId777" ref="K460"/>
+    <hyperlink r:id="rId778" ref="AJ460"/>
+    <hyperlink r:id="rId779" ref="K461"/>
+    <hyperlink r:id="rId780" ref="AJ461"/>
+    <hyperlink r:id="rId781" ref="K462"/>
+    <hyperlink r:id="rId782" ref="AJ462"/>
+    <hyperlink r:id="rId783" ref="K463"/>
+    <hyperlink r:id="rId784" ref="Y463"/>
+    <hyperlink r:id="rId785" ref="AJ463"/>
+    <hyperlink r:id="rId786" ref="K464"/>
+    <hyperlink r:id="rId787" ref="AJ464"/>
+    <hyperlink r:id="rId788" ref="K465"/>
+    <hyperlink r:id="rId789" ref="AJ465"/>
+    <hyperlink r:id="rId790" ref="K466"/>
+    <hyperlink r:id="rId791" ref="AJ466"/>
+    <hyperlink r:id="rId792" ref="K468"/>
+    <hyperlink r:id="rId793" ref="AG468"/>
+    <hyperlink r:id="rId794" ref="AJ468"/>
+    <hyperlink r:id="rId795" ref="K469"/>
+    <hyperlink r:id="rId796" ref="AJ469"/>
+    <hyperlink r:id="rId797" ref="AT469"/>
+    <hyperlink r:id="rId798" ref="K470"/>
+    <hyperlink r:id="rId799" ref="AJ470"/>
+    <hyperlink r:id="rId800" ref="K471"/>
+    <hyperlink r:id="rId801" ref="AJ471"/>
+    <hyperlink r:id="rId802" ref="K473"/>
+    <hyperlink r:id="rId803" ref="K475"/>
+    <hyperlink r:id="rId804" ref="AJ475"/>
+    <hyperlink r:id="rId805" ref="K477"/>
+    <hyperlink r:id="rId806" ref="AJ477"/>
+    <hyperlink r:id="rId807" ref="K478"/>
+    <hyperlink r:id="rId808" ref="Y478"/>
+    <hyperlink r:id="rId809" ref="AJ478"/>
+    <hyperlink r:id="rId810" ref="K479"/>
+    <hyperlink r:id="rId811" ref="AJ479"/>
+    <hyperlink r:id="rId812" ref="K480"/>
+    <hyperlink r:id="rId813" ref="AJ480"/>
+    <hyperlink r:id="rId814" ref="K481"/>
+    <hyperlink r:id="rId815" ref="AJ481"/>
+    <hyperlink r:id="rId816" ref="K482"/>
+    <hyperlink r:id="rId817" ref="AJ482"/>
+    <hyperlink r:id="rId818" ref="AK483"/>
+    <hyperlink r:id="rId819" ref="K484"/>
+    <hyperlink r:id="rId820" ref="K485"/>
+    <hyperlink r:id="rId821" ref="AJ485"/>
+    <hyperlink r:id="rId822" ref="K486"/>
+    <hyperlink r:id="rId823" ref="AJ486"/>
+    <hyperlink r:id="rId824" ref="K487"/>
+    <hyperlink r:id="rId825" ref="AJ487"/>
+    <hyperlink r:id="rId826" ref="K488"/>
+    <hyperlink r:id="rId827" ref="AJ488"/>
+    <hyperlink r:id="rId828" ref="K489"/>
+    <hyperlink r:id="rId829" ref="AK489"/>
+    <hyperlink r:id="rId830" ref="K490"/>
+    <hyperlink r:id="rId831" ref="AJ490"/>
+    <hyperlink r:id="rId832" ref="K491"/>
+    <hyperlink r:id="rId833" ref="AJ491"/>
+    <hyperlink r:id="rId834" ref="K492"/>
+    <hyperlink r:id="rId835" ref="AJ492"/>
+    <hyperlink r:id="rId836" ref="K493"/>
+    <hyperlink r:id="rId837" ref="AJ493"/>
+    <hyperlink r:id="rId838" ref="K494"/>
+    <hyperlink r:id="rId839" ref="K495"/>
+    <hyperlink r:id="rId840" ref="AJ495"/>
+    <hyperlink r:id="rId841" ref="K496"/>
+    <hyperlink r:id="rId842" ref="AJ496"/>
+    <hyperlink r:id="rId843" ref="K497"/>
+    <hyperlink r:id="rId844" ref="AJ497"/>
+    <hyperlink r:id="rId845" ref="AT499"/>
+    <hyperlink r:id="rId846" ref="K500"/>
+    <hyperlink r:id="rId847" ref="AJ500"/>
+    <hyperlink r:id="rId848" ref="K501"/>
+    <hyperlink r:id="rId849" ref="AJ501"/>
+    <hyperlink r:id="rId850" ref="K502"/>
+    <hyperlink r:id="rId851" ref="AJ502"/>
+    <hyperlink r:id="rId852" ref="K503"/>
+    <hyperlink r:id="rId853" ref="Y503"/>
+    <hyperlink r:id="rId854" ref="AJ503"/>
+    <hyperlink r:id="rId855" ref="K504"/>
+    <hyperlink r:id="rId856" ref="AJ504"/>
+    <hyperlink r:id="rId857" ref="K505"/>
+    <hyperlink r:id="rId858" ref="AJ505"/>
+    <hyperlink r:id="rId859" ref="K506"/>
+    <hyperlink r:id="rId860" ref="AJ506"/>
+    <hyperlink r:id="rId861" ref="K507"/>
+    <hyperlink r:id="rId862" ref="AJ507"/>
+    <hyperlink r:id="rId863" ref="K508"/>
+    <hyperlink r:id="rId864" ref="AJ508"/>
+    <hyperlink r:id="rId865" ref="K509"/>
+    <hyperlink r:id="rId866" ref="AJ509"/>
+    <hyperlink r:id="rId867" ref="AT509"/>
+    <hyperlink r:id="rId868" ref="K510"/>
+    <hyperlink r:id="rId869" ref="AJ510"/>
+    <hyperlink r:id="rId870" ref="K511"/>
+    <hyperlink r:id="rId871" ref="AJ511"/>
+    <hyperlink r:id="rId872" ref="K512"/>
+    <hyperlink r:id="rId873" ref="AJ512"/>
+    <hyperlink r:id="rId874" ref="K513"/>
+    <hyperlink r:id="rId875" ref="AJ513"/>
+    <hyperlink r:id="rId876" ref="K514"/>
+    <hyperlink r:id="rId877" ref="Y514"/>
+    <hyperlink r:id="rId878" ref="AJ514"/>
+    <hyperlink r:id="rId879" ref="K515"/>
+    <hyperlink r:id="rId880" ref="Y515"/>
+    <hyperlink r:id="rId881" ref="AJ515"/>
+    <hyperlink r:id="rId882" ref="K516"/>
+    <hyperlink r:id="rId883" ref="AJ516"/>
+    <hyperlink r:id="rId884" ref="K517"/>
+    <hyperlink r:id="rId885" ref="AJ517"/>
+    <hyperlink r:id="rId886" ref="K518"/>
+    <hyperlink r:id="rId887" ref="AJ518"/>
+    <hyperlink r:id="rId888" ref="K519"/>
+    <hyperlink r:id="rId889" ref="AJ519"/>
+    <hyperlink r:id="rId890" ref="AT519"/>
+    <hyperlink r:id="rId891" ref="K520"/>
+    <hyperlink r:id="rId892" ref="AT520"/>
+    <hyperlink r:id="rId893" ref="K521"/>
+    <hyperlink r:id="rId894" ref="AJ521"/>
+    <hyperlink r:id="rId895" ref="AT521"/>
+    <hyperlink r:id="rId896" ref="AJ522"/>
+    <hyperlink r:id="rId897" ref="K523"/>
+    <hyperlink r:id="rId898" ref="AJ523"/>
+    <hyperlink r:id="rId899" ref="K525"/>
+    <hyperlink r:id="rId900" ref="AJ525"/>
+    <hyperlink r:id="rId901" ref="K526"/>
+    <hyperlink r:id="rId902" ref="AJ526"/>
+    <hyperlink r:id="rId903" ref="K528"/>
+    <hyperlink r:id="rId904" ref="AJ528"/>
+    <hyperlink r:id="rId905" ref="K529"/>
+    <hyperlink r:id="rId906" ref="AJ529"/>
+    <hyperlink r:id="rId907" ref="AT532"/>
+    <hyperlink r:id="rId908" ref="K533"/>
+    <hyperlink r:id="rId909" ref="AJ533"/>
+    <hyperlink r:id="rId910" ref="K534"/>
+    <hyperlink r:id="rId911" ref="AJ534"/>
+    <hyperlink r:id="rId912" ref="K535"/>
+    <hyperlink r:id="rId913" ref="AJ535"/>
+    <hyperlink r:id="rId914" ref="K536"/>
+    <hyperlink r:id="rId915" ref="AJ536"/>
+    <hyperlink r:id="rId916" ref="K537"/>
+    <hyperlink r:id="rId917" ref="AJ537"/>
+    <hyperlink r:id="rId918" ref="K538"/>
+    <hyperlink r:id="rId919" ref="AJ538"/>
+    <hyperlink r:id="rId920" ref="K539"/>
+    <hyperlink r:id="rId921" ref="AJ539"/>
+    <hyperlink r:id="rId922" ref="K540"/>
+    <hyperlink r:id="rId923" ref="AK540"/>
+    <hyperlink r:id="rId924" ref="K541"/>
+    <hyperlink r:id="rId925" ref="AJ541"/>
+    <hyperlink r:id="rId926" ref="K542"/>
+    <hyperlink r:id="rId927" ref="AJ542"/>
+    <hyperlink r:id="rId928" ref="K543"/>
+    <hyperlink r:id="rId929" ref="AJ543"/>
+    <hyperlink r:id="rId930" ref="K544"/>
+    <hyperlink r:id="rId931" ref="AJ544"/>
+    <hyperlink r:id="rId932" ref="K545"/>
+    <hyperlink r:id="rId933" ref="AJ545"/>
+    <hyperlink r:id="rId934" ref="K546"/>
+    <hyperlink r:id="rId935" ref="AJ546"/>
+    <hyperlink r:id="rId936" ref="AT546"/>
+    <hyperlink r:id="rId937" ref="K547"/>
+    <hyperlink r:id="rId938" ref="Y547"/>
+    <hyperlink r:id="rId939" ref="AJ547"/>
+    <hyperlink r:id="rId940" ref="K548"/>
+    <hyperlink r:id="rId941" ref="AJ548"/>
   </hyperlinks>
   <printOptions/>
   <pageMargins bottom="0.984027777777778" footer="0.0" header="0.0" left="0.747916666666667" right="0.747916666666667" top="0.984027777777778"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <drawing r:id="rId943"/>
+  <drawing r:id="rId942"/>
 </worksheet>
 </file>